--- a/基本設計/14_日報と通知_API基本設計書.xlsx
+++ b/基本設計/14_日報と通知_API基本設計書.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Rf5ae33b61b9740ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Raff7ff8937874309"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_API一覧" sheetId="19" r:id="Rdf0e46ac7b124152"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_エラーコード" sheetId="22" r:id="R901501bb52374f68"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_API主要項目処理" sheetId="23" r:id="R12fe489aa9814329"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_API処理・権限" sheetId="24" r:id="R9646883fa0194887"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_API項目定義" sheetId="25" r:id="R65cae3e8303a48fb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_APIサンプル" sheetId="26" r:id="Redf23117c6f64e60"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25_API権限対応" sheetId="27" r:id="R5aa8ea102d05476a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R57329becb9f545b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R74c84291043142c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_API一覧" sheetId="19" r:id="R7d46e3e901824fc4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_エラーコード" sheetId="22" r:id="R16e1cc0ddea5455e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_API主要項目処理" sheetId="23" r:id="R7b2a67f22c974aa5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_API処理・権限" sheetId="24" r:id="R5c836a9a5bf4417e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_API項目定義" sheetId="25" r:id="Ra840ea3fdee84ea4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_APIサンプル" sheetId="26" r:id="R9a492058efea4e57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25_API権限対応" sheetId="27" r:id="Redb98b1cb8a048a9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1297,10 +1297,7 @@
       <x:c r="F16" s="196"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" t="str">
-        <x:v>本書は Company WorkHub の基本設計内容を定義する。
-Ver.1.8 は状態変更入口、API/DB制約、取込Transaction、日報一意制約、通知・Token保持を整合した再Review対応版である。</x:v>
-      </x:c>
+      <x:c r="A17"/>
       <x:c r="C17"/>
       <x:c r="D17"/>
       <x:c r="E17"/>
@@ -1316,25 +1313,22 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19"/>
-      <x:c r="B19" s="240" t="str">
-        <x:v>本書は Company WorkHub の基本設計内容を定義する。
-Ver.1.7 は状態変更入口、API/DB制約、取込Transaction、日報一意制約、通知・Token保持を整合した再Review対応版である。</x:v>
-      </x:c>
-      <x:c r="C19" s="240"/>
-      <x:c r="D19" s="240"/>
-      <x:c r="E19" s="240"/>
-      <x:c r="F19" s="240"/>
-      <x:c r="G19" s="240"/>
-      <x:c r="H19" s="240"/>
+      <x:c r="B19"/>
+      <x:c r="C19"/>
+      <x:c r="D19"/>
+      <x:c r="E19"/>
+      <x:c r="F19"/>
+      <x:c r="G19"/>
+      <x:c r="H19"/>
     </x:row>
     <x:row r="20">
-      <x:c r="B20" s="240"/>
-      <x:c r="C20" s="240"/>
-      <x:c r="D20" s="240"/>
-      <x:c r="E20" s="240"/>
-      <x:c r="F20" s="240"/>
-      <x:c r="G20" s="240"/>
-      <x:c r="H20" s="240"/>
+      <x:c r="B20"/>
+      <x:c r="C20"/>
+      <x:c r="D20"/>
+      <x:c r="E20"/>
+      <x:c r="F20"/>
+      <x:c r="G20"/>
+      <x:c r="H20"/>
     </x:row>
     <x:row r="21">
       <x:c r="B21" s="240"/>
@@ -3520,17 +3514,15 @@
       <x:c r="I18" s="64"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="88" t="str">
-        <x:v>Class名、Method名、SQLは詳細設計で定義する。ただし本SheetのURL、I/O、権限、Data範囲、Error契約はPG判断で変更しない。</x:v>
-      </x:c>
-      <x:c r="B19" s="89"/>
-      <x:c r="C19" s="89"/>
-      <x:c r="D19" s="89"/>
-      <x:c r="E19" s="89"/>
-      <x:c r="F19" s="89"/>
-      <x:c r="G19" s="89"/>
-      <x:c r="H19" s="89"/>
-      <x:c r="I19" s="90"/>
+      <x:c r="A19"/>
+      <x:c r="B19"/>
+      <x:c r="C19"/>
+      <x:c r="D19"/>
+      <x:c r="E19"/>
+      <x:c r="F19"/>
+      <x:c r="G19"/>
+      <x:c r="H19"/>
+      <x:c r="I19"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="91"/>

--- a/基本設計/14_日報と通知_API基本設計書.xlsx
+++ b/基本設計/14_日報と通知_API基本設計書.xlsx
@@ -2,15 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R57329becb9f545b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R74c84291043142c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_API一覧" sheetId="19" r:id="R7d46e3e901824fc4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_エラーコード" sheetId="22" r:id="R16e1cc0ddea5455e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_API主要項目処理" sheetId="23" r:id="R7b2a67f22c974aa5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_API処理・権限" sheetId="24" r:id="R5c836a9a5bf4417e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_API項目定義" sheetId="25" r:id="Ra840ea3fdee84ea4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_APIサンプル" sheetId="26" r:id="R9a492058efea4e57"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25_API権限対応" sheetId="27" r:id="Redb98b1cb8a048a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R1040268f341a4c0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R7f037447b0b84dea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_API一覧" sheetId="19" r:id="R9aa9c5ce0d0c47c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_エラーコード" sheetId="22" r:id="Rafdbddf691d44b6c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_API処理・権限" sheetId="24" r:id="R67ce2d0546f042d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_API項目定義" sheetId="25" r:id="Rc817cb6fbd994bc7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_APIサンプル" sheetId="26" r:id="R0d3a6c3c608d49bd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -24,7 +22,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
   </x:numFmts>
-  <x:fonts count="25">
+  <x:fonts count="27">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -163,8 +161,19 @@
       <x:color rgb="FF1F1F1F"/>
       <x:name val="Yu Gothic"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF18283A"/>
+      <x:name val="Yu Gothic"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="17"/>
+      <x:color rgb="FF193C61"/>
+      <x:name val="Yu Gothic"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="29">
+  <x:fills count="31">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -306,8 +315,18 @@
         <x:fgColor rgb="FFFFF2CC"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF234F77"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF1F5FA"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="8">
+  <x:borders count="9">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -365,11 +384,25 @@
         <x:color rgb="FFA6A6A6"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD4DEE8"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD4DEE8"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD4DEE8"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD4DEE8"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="241">
+  <x:cellXfs count="257">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -867,6 +900,50 @@
     <x:xf numFmtId="0" fontId="24" fillId="28" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="30" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -1235,8 +1312,8 @@
     </x:row>
     <x:row r="11">
       <x:c r="B11"/>
-      <x:c r="C11" t="str">
-        <x:v>Ver.1.8</x:v>
+      <x:c r="C11" s="203" t="str">
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="D11"/>
       <x:c r="E11"/>
@@ -1245,8 +1322,8 @@
       <x:c r="H11"/>
     </x:row>
     <x:row r="12">
-      <x:c r="C12" s="235" t="str">
-        <x:v>文書番号</x:v>
+      <x:c r="C12" s="242" t="str">
+        <x:v>Document ID</x:v>
       </x:c>
       <x:c r="D12" s="196" t="str">
         <x:v>CW-BD-API-RPT</x:v>
@@ -1258,8 +1335,8 @@
       <x:c r="C13" s="235" t="str">
         <x:v>版数</x:v>
       </x:c>
-      <x:c r="D13" s="196" t="str">
-        <x:v>Ver.1.8</x:v>
+      <x:c r="D13" s="243" t="str">
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="E13" s="196"/>
       <x:c r="F13" s="196"/>
@@ -1268,8 +1345,8 @@
       <x:c r="C14" s="235" t="str">
         <x:v>改訂日</x:v>
       </x:c>
-      <x:c r="D14" s="196" t="str">
-        <x:v>2026-08-12</x:v>
+      <x:c r="D14" s="243" t="str">
+        <x:v>2026-09-24</x:v>
       </x:c>
       <x:c r="E14" s="196"/>
       <x:c r="F14" s="196"/>
@@ -1290,24 +1367,29 @@
       <x:c r="C16" s="235" t="str">
         <x:v>状態</x:v>
       </x:c>
-      <x:c r="D16" s="196" t="str">
-        <x:v>レビュー待ち</x:v>
+      <x:c r="D16" s="243" t="str">
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="E16" s="196"/>
       <x:c r="F16" s="196"/>
     </x:row>
-    <x:row r="17">
-      <x:c r="A17"/>
-      <x:c r="C17"/>
-      <x:c r="D17"/>
+    <x:row r="17" ht="26" customHeight="1">
+      <x:c r="A17" s="245"/>
+      <x:c r="B17" s="245"/>
+      <x:c r="C17" s="245"/>
+      <x:c r="D17" s="245"/>
       <x:c r="E17"/>
       <x:c r="F17"/>
     </x:row>
-    <x:row r="18">
-      <x:c r="A18"/>
-      <x:c r="B18"/>
-      <x:c r="C18"/>
-      <x:c r="D18"/>
+    <x:row r="18" ht="26" customHeight="1">
+      <x:c r="A18" s="245"/>
+      <x:c r="B18" s="245"/>
+      <x:c r="C18" s="245" t="str">
+        <x:v>Baseline ID</x:v>
+      </x:c>
+      <x:c r="D18" s="245" t="str">
+        <x:v>BL-2026-09-24</x:v>
+      </x:c>
       <x:c r="E18"/>
       <x:c r="F18"/>
     </x:row>
@@ -1415,41 +1497,29 @@
       <x:c r="G2" s="172"/>
       <x:c r="H2" s="172"/>
     </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="174" t="str">
-        <x:v>システム名</x:v>
-      </x:c>
-      <x:c r="B3" s="139" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="C3" s="139"/>
-      <x:c r="D3" s="174" t="str">
-        <x:v>文書番号</x:v>
-      </x:c>
-      <x:c r="E3" s="139" t="str">
-        <x:v>DOCUMENT-REVISION</x:v>
-      </x:c>
-      <x:c r="F3" s="139"/>
-      <x:c r="G3" s="139"/>
-      <x:c r="H3" s="139"/>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="174" t="str">
-        <x:v>版数</x:v>
-      </x:c>
-      <x:c r="B4" s="139" t="str">
-        <x:v>Ver.1.8</x:v>
-      </x:c>
-      <x:c r="C4" s="139"/>
-      <x:c r="D4" s="174" t="str">
-        <x:v>改訂日</x:v>
-      </x:c>
-      <x:c r="E4" s="139" t="str">
-        <x:v>2026-08-12</x:v>
-      </x:c>
-      <x:c r="F4" s="139"/>
-      <x:c r="G4" s="139"/>
-      <x:c r="H4" s="139"/>
+    <x:row r="3" ht="24" customHeight="1">
+      <x:c r="A3" s="246" t="str">
+        <x:v>システム名：Company WorkHub</x:v>
+      </x:c>
+      <x:c r="B3" s="63"/>
+      <x:c r="C3" s="63"/>
+      <x:c r="D3" s="246"/>
+      <x:c r="E3" s="63"/>
+      <x:c r="F3" s="63"/>
+      <x:c r="G3" s="63"/>
+      <x:c r="H3" s="63"/>
+    </x:row>
+    <x:row r="4" ht="24" customHeight="1">
+      <x:c r="A4" s="246" t="str">
+        <x:v>版数：Ver.2.5    改訂日：2026-09-24    Baseline：BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="B4" s="63"/>
+      <x:c r="C4" s="63"/>
+      <x:c r="D4" s="246"/>
+      <x:c r="E4" s="63"/>
+      <x:c r="F4" s="63"/>
+      <x:c r="G4" s="63"/>
+      <x:c r="H4" s="63"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5"/>
@@ -1481,7 +1551,7 @@
         <x:v>改訂日</x:v>
       </x:c>
       <x:c r="C7" s="181" t="str">
-        <x:v>2026-08-12</x:v>
+        <x:v>改訂内容</x:v>
       </x:c>
       <x:c r="D7" s="181" t="str">
         <x:v>作成者</x:v>
@@ -1519,7 +1589,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G8" s="67" t="str">
-        <x:v>作成済</x:v>
+        <x:v>作成中</x:v>
       </x:c>
       <x:c r="H8" s="67" t="str">
         <x:v>基本設計初版</x:v>
@@ -1545,7 +1615,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G9" s="67" t="str">
-        <x:v>レビュー待ち</x:v>
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H9" s="67" t="str">
         <x:v>Leader Review後Baseline化</x:v>
@@ -1571,7 +1641,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G10" s="67" t="str">
-        <x:v>レビュー待ち</x:v>
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H10" s="67" t="str">
         <x:v>Review指摘対応</x:v>
@@ -1597,7 +1667,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G11" s="67" t="str">
-        <x:v>レビュー待ち</x:v>
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H11" s="67" t="str">
         <x:v>再監査指摘対応</x:v>
@@ -1623,7 +1693,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G12" s="67" t="str">
-        <x:v>レビュー待ち</x:v>
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H12" s="67" t="str">
         <x:v>再監査第2回指摘対応</x:v>
@@ -1648,8 +1718,8 @@
       <x:c r="F13" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="G13" t="str">
-        <x:v>レビュー待ち</x:v>
+      <x:c r="G13" s="203" t="str">
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H13" t="str">
         <x:v>再監査残項対応</x:v>
@@ -1674,8 +1744,8 @@
       <x:c r="F14" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="G14" t="str">
-        <x:v>レビュー待ち</x:v>
+      <x:c r="G14" s="203" t="str">
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H14" t="str">
         <x:v>再Review指摘対応</x:v>
@@ -1700,25 +1770,153 @@
       <x:c r="F15" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="G15" t="str">
-        <x:v>レビュー待ち</x:v>
+      <x:c r="G15" s="203" t="str">
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H15" t="str">
         <x:v>最大10回の反復監査対応</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>1.9</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>2026-08-17</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>未読件数APIの利用元を共通Headerへ統一</x:v>
+      </x:c>
+      <x:c r="D16" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="E16" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="F16" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="G16" s="203" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H16" t="str">
+        <x:v>04再Review影響反映</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>2.0</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>七項目Review指摘対応：画面・API・DB項目、論理削除、認証限流、日報関連Task、Baseline判定を整合</x:v>
+      </x:c>
+      <x:c r="D17" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="E17" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="F17" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="G17" t="str">
+        <x:v>レビュー済</x:v>
+      </x:c>
+      <x:c r="H17" t="str">
+        <x:v>Leader最終承認待ち</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="110" customHeight="1">
+      <x:c r="A18" s="241" t="str">
+        <x:v>Ver.2.3</x:v>
+      </x:c>
+      <x:c r="B18" s="241" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="C18" s="241" t="str">
+        <x:v>内容・関連Reviewの既確定仕様を整合。業務未決事項は承認待ちとして管理。</x:v>
+      </x:c>
+      <x:c r="D18" s="241" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="E18" s="241" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="F18" s="241" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="G18" s="241" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H18" s="241" t="str">
+        <x:v>2026-09-18指摘対応。正式承認を示すものではない。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="40" customHeight="1">
+      <x:c r="A19" s="241" t="str">
+        <x:v>Ver.2.4</x:v>
+      </x:c>
+      <x:c r="B19" s="241" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="C19" s="241" t="str">
+        <x:v>待確認12項目の方針選定、業務/API/DB/画面/運用を連動修正。章立て維持。</x:v>
+      </x:c>
+      <x:c r="D19" s="241" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="E19" s="241" t="str">
+        <x:v>未実施</x:v>
+      </x:c>
+      <x:c r="F19" s="241" t="str">
+        <x:v>未承認</x:v>
+      </x:c>
+      <x:c r="G19" s="241" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H19" s="241" t="str">
+        <x:v>一般社内管理Systemの範囲。旧版はBackup保管。</x:v>
+      </x:c>
+      <x:c r="I19" s="241"/>
+      <x:c r="J19" s="241"/>
+      <x:c r="K19" s="241"/>
+      <x:c r="L19" s="241"/>
+    </x:row>
+    <x:row r="20" ht="100" customHeight="1">
+      <x:c r="A20" s="245" t="str">
+        <x:v>Ver.2.5</x:v>
+      </x:c>
+      <x:c r="B20" s="245" t="str">
+        <x:v>2026-09-24</x:v>
+      </x:c>
+      <x:c r="C20" s="245" t="str">
+        <x:v>共通規則・正本参照・構成・文書管理を統合修正。Baseline承認前の最終整合修正。</x:v>
+      </x:c>
+      <x:c r="D20" s="245" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="E20" s="245" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="F20" s="245" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="G20" s="245" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="H20" s="245" t="str">
+        <x:v>BL-2026-09-24。責任者・Review者・承認者はProject Leaderが記入。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:H2"/>
-    <x:mergeCell ref="A3:B3"/>
-    <x:mergeCell ref="C3:D3"/>
-    <x:mergeCell ref="E3:F3"/>
-    <x:mergeCell ref="G3:H3"/>
-    <x:mergeCell ref="A4:B4"/>
-    <x:mergeCell ref="C4:D4"/>
-    <x:mergeCell ref="E4:F4"/>
-    <x:mergeCell ref="G4:H4"/>
     <x:mergeCell ref="A6:H6"/>
+    <x:mergeCell ref="A3:H3"/>
+    <x:mergeCell ref="A4:H4"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -1767,36 +1965,28 @@
       <x:c r="A3" s="62" t="str">
         <x:v>システム名</x:v>
       </x:c>
-      <x:c r="B3" s="63" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
+      <x:c r="B3" s="63" t="str"/>
       <x:c r="C3" s="63"/>
       <x:c r="D3" s="63"/>
-      <x:c r="E3" s="62" t="str">
-        <x:v>文書番号</x:v>
-      </x:c>
-      <x:c r="F3" s="63" t="str">
-        <x:v>CW-BD-API-RPT-LIST</x:v>
-      </x:c>
+      <x:c r="E3" s="246" t="str">
+        <x:v>章ID</x:v>
+      </x:c>
+      <x:c r="F3" s="63" t="str"/>
       <x:c r="G3" s="63"/>
       <x:c r="H3" s="63"/>
       <x:c r="I3" s="63"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="62" t="str">
-        <x:v>版数</x:v>
-      </x:c>
-      <x:c r="B4" s="63" t="str">
-        <x:v>Ver.1.8</x:v>
-      </x:c>
+      <x:c r="A4" s="246" t="str">
+        <x:v>版数：Ver.2.5</x:v>
+      </x:c>
+      <x:c r="B4" s="63"/>
       <x:c r="C4" s="63"/>
       <x:c r="D4" s="63"/>
-      <x:c r="E4" s="62" t="str">
-        <x:v>改訂日</x:v>
-      </x:c>
-      <x:c r="F4" s="63" t="str">
-        <x:v>2026-08-12</x:v>
-      </x:c>
+      <x:c r="E4" s="246" t="str">
+        <x:v>改訂日：2026-09-24</x:v>
+      </x:c>
+      <x:c r="F4" s="63"/>
       <x:c r="G4" s="63"/>
       <x:c r="H4" s="63"/>
       <x:c r="I4" s="63"/>
@@ -1854,7 +2044,7 @@
         <x:v>Error Code</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="30" customHeight="1">
+    <x:row r="8" ht="39" customHeight="1">
       <x:c r="A8" s="67" t="str">
         <x:v>API-RPT-001</x:v>
       </x:c>
@@ -1868,22 +2058,22 @@
         <x:v>日報検索</x:v>
       </x:c>
       <x:c r="E8" s="67" t="str">
-        <x:v>権限別</x:v>
+        <x:v>02／13_API権限対応：API-RPT-001</x:v>
       </x:c>
       <x:c r="F8" s="67" t="str">
-        <x:v>query: employeeId,departmentId,projectId,dateFrom,dateTo,hasIssue,missing,page,size,sort</x:v>
+        <x:v>23_API項目定義：API-RPT-001 Request</x:v>
       </x:c>
       <x:c r="G8" s="67" t="str">
-        <x:v>Page&lt;DailyReportSummary&gt;</x:v>
+        <x:v>23_API項目定義：API-RPT-001 Response（正本）</x:v>
       </x:c>
       <x:c r="H8" s="67" t="str">
         <x:v>SCR-019, SCR-021</x:v>
       </x:c>
       <x:c r="I8" s="67" t="str">
-        <x:v>COMMON-4000/AUTH-4006</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F8／21_エラーコード</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="39" customHeight="1">
       <x:c r="A9" s="67" t="str">
         <x:v>API-RPT-002</x:v>
       </x:c>
@@ -1897,22 +2087,22 @@
         <x:v>日報詳細</x:v>
       </x:c>
       <x:c r="E9" s="67" t="str">
-        <x:v>権限別</x:v>
+        <x:v>02／13_API権限対応：API-RPT-002</x:v>
       </x:c>
       <x:c r="F9" s="67" t="str">
-        <x:v>path: id Long</x:v>
+        <x:v>23_API項目定義：API-RPT-002 Request</x:v>
       </x:c>
       <x:c r="G9" s="67" t="str">
-        <x:v>DailyReportDetail + tasks[]</x:v>
+        <x:v>23_API項目定義：API-RPT-002 Response（正本）</x:v>
       </x:c>
       <x:c r="H9" s="67" t="str">
         <x:v>SCR-019, SCR-020, SCR-021</x:v>
       </x:c>
       <x:c r="I9" s="67" t="str">
-        <x:v>COMMON-4040/AUTH-4006</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F9／21_エラーコード</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="39" customHeight="1">
       <x:c r="A10" s="67" t="str">
         <x:v>API-RPT-003</x:v>
       </x:c>
@@ -1926,22 +2116,22 @@
         <x:v>日報登録</x:v>
       </x:c>
       <x:c r="E10" s="67" t="str">
-        <x:v>全員</x:v>
+        <x:v>02／13_API権限対応：API-RPT-003</x:v>
       </x:c>
       <x:c r="F10" s="67" t="str">
-        <x:v>body: reportDate,projectId,completedWork,plannedWork,issues,workingHours,taskIds[]; header: X-Idempotency-Key</x:v>
+        <x:v>23_API項目定義：API-RPT-003 Request</x:v>
       </x:c>
       <x:c r="G10" s="67" t="str">
-        <x:v>id,version</x:v>
+        <x:v>23_API項目定義：API-RPT-003 Response（正本）</x:v>
       </x:c>
       <x:c r="H10" s="67" t="str">
         <x:v>SCR-020</x:v>
       </x:c>
       <x:c r="I10" s="67" t="str">
-        <x:v>RPT-4001, RPT-4002,COMMON-4090</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F10／21_エラーコード</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="39" customHeight="1">
       <x:c r="A11" s="67" t="str">
         <x:v>API-RPT-004</x:v>
       </x:c>
@@ -1955,22 +2145,22 @@
         <x:v>日報更新</x:v>
       </x:c>
       <x:c r="E11" s="67" t="str">
-        <x:v>本人/管理者</x:v>
+        <x:v>02／13_API権限対応：API-RPT-004</x:v>
       </x:c>
       <x:c r="F11" s="67" t="str">
-        <x:v>path: id; body: completedWork,plannedWork,issues,workingHours,taskIds[],version</x:v>
+        <x:v>23_API項目定義：API-RPT-004 Request</x:v>
       </x:c>
       <x:c r="G11" s="67" t="str">
-        <x:v>id,version</x:v>
+        <x:v>23_API項目定義：API-RPT-004 Response（正本）</x:v>
       </x:c>
       <x:c r="H11" s="67" t="str">
         <x:v>SCR-020</x:v>
       </x:c>
       <x:c r="I11" s="67" t="str">
-        <x:v>RPT-4002,COMMON-4040, COMMON-4090</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F11／21_エラーコード</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="39" customHeight="1">
       <x:c r="A12" s="67" t="str">
         <x:v>API-RPT-005</x:v>
       </x:c>
@@ -1984,22 +2174,22 @@
         <x:v>日報削除</x:v>
       </x:c>
       <x:c r="E12" s="67" t="str">
-        <x:v>本人/管理者</x:v>
+        <x:v>02／13_API権限対応：API-RPT-005</x:v>
       </x:c>
       <x:c r="F12" s="67" t="str">
-        <x:v>path: id; query: version</x:v>
+        <x:v>23_API項目定義：API-RPT-005 Request</x:v>
       </x:c>
       <x:c r="G12" s="67" t="str">
-        <x:v>204 No Content</x:v>
+        <x:v>23_API項目定義：API-RPT-005 Response（正本）</x:v>
       </x:c>
       <x:c r="H12" s="67" t="str">
         <x:v>SCR-019, SCR-020</x:v>
       </x:c>
       <x:c r="I12" s="67" t="str">
-        <x:v>RPT-4002,COMMON-4090</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F12／21_エラーコード</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="39" customHeight="1">
       <x:c r="A13" s="67" t="str">
         <x:v>API-RPT-006</x:v>
       </x:c>
@@ -2013,22 +2203,22 @@
         <x:v>未提出者検索</x:v>
       </x:c>
       <x:c r="E13" s="67" t="str">
-        <x:v>管理者/担当PM</x:v>
+        <x:v>02／13_API権限対応：API-RPT-006</x:v>
       </x:c>
       <x:c r="F13" s="67" t="str">
-        <x:v>query: date,projectId,page,size</x:v>
+        <x:v>23_API項目定義：API-RPT-006 Request</x:v>
       </x:c>
       <x:c r="G13" s="67" t="str">
-        <x:v>Page&lt;EmployeeSummary&gt;</x:v>
+        <x:v>23_API項目定義：API-RPT-006 Response（正本）</x:v>
       </x:c>
       <x:c r="H13" s="67" t="str">
         <x:v>SCR-021</x:v>
       </x:c>
       <x:c r="I13" s="67" t="str">
-        <x:v>COMMON-4000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F13／21_エラーコード</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="39" customHeight="1">
       <x:c r="A14" s="67" t="str">
         <x:v>API-NTF-001</x:v>
       </x:c>
@@ -2042,22 +2232,22 @@
         <x:v>通知一覧</x:v>
       </x:c>
       <x:c r="E14" s="67" t="str">
-        <x:v>全員</x:v>
+        <x:v>02／13_API権限対応：API-NTF-001</x:v>
       </x:c>
       <x:c r="F14" s="67" t="str">
-        <x:v>query: read,type,page,size,sort</x:v>
+        <x:v>23_API項目定義：API-NTF-001 Request</x:v>
       </x:c>
       <x:c r="G14" s="67" t="str">
-        <x:v>Page&lt;Notification&gt;</x:v>
+        <x:v>23_API項目定義：API-NTF-001 Response（正本）</x:v>
       </x:c>
       <x:c r="H14" s="67" t="str">
         <x:v>SCR-022</x:v>
       </x:c>
       <x:c r="I14" s="67" t="str">
-        <x:v>COMMON-4000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F14／21_エラーコード</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="39" customHeight="1">
       <x:c r="A15" s="67" t="str">
         <x:v>API-NTF-002</x:v>
       </x:c>
@@ -2071,22 +2261,22 @@
         <x:v>未読件数</x:v>
       </x:c>
       <x:c r="E15" s="67" t="str">
-        <x:v>全員</x:v>
+        <x:v>02／13_API権限対応：API-NTF-002</x:v>
       </x:c>
       <x:c r="F15" s="67" t="str">
-        <x:v>なし</x:v>
+        <x:v>23_API項目定義：API-NTF-002 Request</x:v>
       </x:c>
       <x:c r="G15" s="67" t="str">
-        <x:v>count Integer</x:v>
+        <x:v>23_API項目定義：API-NTF-002 Response（正本）</x:v>
       </x:c>
       <x:c r="H15" s="67" t="str">
-        <x:v>共通Header/SCR-002</x:v>
+        <x:v>共通Header</x:v>
       </x:c>
       <x:c r="I15" s="67" t="str">
-        <x:v>COMMON-5000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F15／21_エラーコード</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="39" customHeight="1">
       <x:c r="A16" s="67" t="str">
         <x:v>API-NTF-003</x:v>
       </x:c>
@@ -2100,22 +2290,22 @@
         <x:v>既読化</x:v>
       </x:c>
       <x:c r="E16" s="67" t="str">
-        <x:v>本人</x:v>
+        <x:v>02／13_API権限対応：API-NTF-003</x:v>
       </x:c>
       <x:c r="F16" s="67" t="str">
-        <x:v>path: id</x:v>
+        <x:v>23_API項目定義：API-NTF-003 Request</x:v>
       </x:c>
       <x:c r="G16" s="67" t="str">
-        <x:v>id,isRead,readAt</x:v>
+        <x:v>23_API項目定義：API-NTF-003 Response（正本）</x:v>
       </x:c>
       <x:c r="H16" s="67" t="str">
         <x:v>SCR-022</x:v>
       </x:c>
       <x:c r="I16" s="67" t="str">
-        <x:v>COMMON-4040/AUTH-4006</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F16／21_エラーコード</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="39" customHeight="1">
       <x:c r="A17" s="67" t="str">
         <x:v>API-NTF-004</x:v>
       </x:c>
@@ -2129,19 +2319,19 @@
         <x:v>全件既読</x:v>
       </x:c>
       <x:c r="E17" s="67" t="str">
-        <x:v>本人</x:v>
+        <x:v>02／13_API権限対応：API-NTF-004</x:v>
       </x:c>
       <x:c r="F17" s="67" t="str">
-        <x:v>body: before DateTime?</x:v>
+        <x:v>23_API項目定義：API-NTF-004 Request</x:v>
       </x:c>
       <x:c r="G17" s="67" t="str">
-        <x:v>updatedCount</x:v>
+        <x:v>23_API項目定義：API-NTF-004 Response（正本）</x:v>
       </x:c>
       <x:c r="H17" s="67" t="str">
         <x:v>SCR-022</x:v>
       </x:c>
       <x:c r="I17" s="67" t="str">
-        <x:v>COMMON-4000</x:v>
+        <x:v>22_API処理・権限!F17／21_エラーコード</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -2561,281 +2751,223 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="46" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="50" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="24" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="24" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="24" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="20" t="str">
-        <x:v>業務エラーコード</x:v>
-      </x:c>
-      <x:c r="B1" s="20"/>
-      <x:c r="C1" s="20"/>
-      <x:c r="D1" s="20"/>
-      <x:c r="E1" s="20"/>
-      <x:c r="F1" s="20"/>
-      <x:c r="G1" s="20"/>
-      <x:c r="H1" s="20"/>
+      <x:c r="A1" s="250" t="str">
+        <x:v>21_エラーコード</x:v>
+      </x:c>
+      <x:c r="B1" s="249"/>
+      <x:c r="C1" s="249"/>
+      <x:c r="D1" s="249"/>
+      <x:c r="E1" s="249"/>
+      <x:c r="F1" s="249"/>
+      <x:c r="G1" s="249"/>
+      <x:c r="H1" s="249"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="20"/>
-      <x:c r="B2" s="20"/>
-      <x:c r="C2" s="20"/>
-      <x:c r="D2" s="20"/>
-      <x:c r="E2" s="20"/>
-      <x:c r="F2" s="20"/>
-      <x:c r="G2" s="20"/>
-      <x:c r="H2" s="20"/>
+      <x:c r="A2" s="249"/>
+      <x:c r="B2" s="249"/>
+      <x:c r="C2" s="249"/>
+      <x:c r="D2" s="249"/>
+      <x:c r="E2" s="249"/>
+      <x:c r="F2" s="249"/>
+      <x:c r="G2" s="249"/>
+      <x:c r="H2" s="249"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="23" t="str">
-        <x:v>システム名</x:v>
-      </x:c>
-      <x:c r="B3" s="23"/>
-      <x:c r="C3" s="21" t="str">
+      <x:c r="A3" s="249" t="str">
         <x:v>Company WorkHub</x:v>
       </x:c>
-      <x:c r="D3" s="21"/>
-      <x:c r="E3" s="23" t="str">
-        <x:v>文書番号</x:v>
-      </x:c>
-      <x:c r="F3" s="23"/>
-      <x:c r="G3" s="21" t="str">
-        <x:v>CW-BD-053</x:v>
-      </x:c>
-      <x:c r="H3" s="21"/>
+      <x:c r="B3" s="249"/>
+      <x:c r="C3" s="249"/>
+      <x:c r="D3" s="249"/>
+      <x:c r="E3" s="249"/>
+      <x:c r="F3" s="249"/>
+      <x:c r="G3" s="249"/>
+      <x:c r="H3" s="249"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="23" t="str">
-        <x:v>版数</x:v>
-      </x:c>
-      <x:c r="B4" s="23"/>
-      <x:c r="C4" s="21" t="str">
-        <x:v>Ver.1.8</x:v>
-      </x:c>
-      <x:c r="D4" s="21"/>
-      <x:c r="E4" s="23" t="str">
-        <x:v>作成日</x:v>
-      </x:c>
-      <x:c r="F4" s="23"/>
-      <x:c r="G4" s="24" t="n">
-        <x:v>46239</x:v>
-      </x:c>
-      <x:c r="H4" s="24"/>
+      <x:c r="A4" s="249"/>
+      <x:c r="B4" s="249"/>
+      <x:c r="C4" s="249"/>
+      <x:c r="D4" s="249"/>
+      <x:c r="E4" s="249"/>
+      <x:c r="F4" s="249"/>
+      <x:c r="G4" s="249"/>
+      <x:c r="H4" s="249"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="249" t="str">
+        <x:v>BL-2026-09-24 / Review中</x:v>
+      </x:c>
+      <x:c r="B5" s="249"/>
+      <x:c r="C5" s="249"/>
+      <x:c r="D5" s="249"/>
+      <x:c r="E5" s="249"/>
+      <x:c r="F5" s="249"/>
+      <x:c r="G5" s="249"/>
+      <x:c r="H5" s="249"/>
     </x:row>
     <x:row r="6" ht="22" customHeight="1">
-      <x:c r="A6" s="26" t="str">
-        <x:v>1. Error Code</x:v>
-      </x:c>
-      <x:c r="B6" s="26"/>
-      <x:c r="C6" s="26"/>
-      <x:c r="D6" s="26"/>
-      <x:c r="E6" s="26"/>
-      <x:c r="F6" s="26"/>
-      <x:c r="G6" s="26"/>
-      <x:c r="H6" s="26"/>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="31" t="str">
+      <x:c r="A6" s="249"/>
+      <x:c r="B6" s="249"/>
+      <x:c r="C6" s="249"/>
+      <x:c r="D6" s="249"/>
+      <x:c r="E6" s="249"/>
+      <x:c r="F6" s="249"/>
+      <x:c r="G6" s="249"/>
+      <x:c r="H6" s="249"/>
+    </x:row>
+    <x:row r="7" ht="32" customHeight="1">
+      <x:c r="A7" s="252" t="str">
         <x:v>Error Code</x:v>
       </x:c>
-      <x:c r="B7" s="31" t="str">
+      <x:c r="B7" s="252" t="str">
         <x:v>分類</x:v>
       </x:c>
-      <x:c r="C7" s="31" t="str">
-        <x:v>意味</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="str">
+      <x:c r="C7" s="252" t="str">
+        <x:v>業務上の意味</x:v>
+      </x:c>
+      <x:c r="D7" s="252" t="str">
         <x:v>HTTP Status</x:v>
       </x:c>
-      <x:c r="E7" s="31" t="str">
-        <x:v>画面Message</x:v>
-      </x:c>
-      <x:c r="F7" s="31" t="str">
-        <x:v>記録Level</x:v>
-      </x:c>
-      <x:c r="G7" s="31" t="str">
+      <x:c r="E7" s="252" t="str">
+        <x:v>Message参照</x:v>
+      </x:c>
+      <x:c r="F7" s="252" t="str">
+        <x:v>Log Level</x:v>
+      </x:c>
+      <x:c r="G7" s="252" t="str">
         <x:v>再試行</x:v>
       </x:c>
-      <x:c r="H7" s="31" t="str">
+      <x:c r="H7" s="252" t="str">
         <x:v>備考</x:v>
       </x:c>
     </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="33" t="str">
-        <x:v>COMMON-0000</x:v>
-      </x:c>
-      <x:c r="B8" s="33" t="str">
-        <x:v>成功</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="str">
-        <x:v>処理成功</x:v>
-      </x:c>
-      <x:c r="D8" s="33" t="n">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="E8" s="33" t="str">
-        <x:v>処理成功</x:v>
-      </x:c>
-      <x:c r="F8" s="33" t="str">
-        <x:v>INFO</x:v>
-      </x:c>
-      <x:c r="G8" s="33" t="str">
-        <x:v>不可</x:v>
-      </x:c>
-      <x:c r="H8" s="33"/>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="33" t="str">
-        <x:v>COMMON-4000</x:v>
-      </x:c>
-      <x:c r="B9" s="33" t="str">
-        <x:v>入力</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="str">
-        <x:v>Request parameter error</x:v>
-      </x:c>
-      <x:c r="D9" s="33" t="n">
+    <x:row r="8" ht="42" customHeight="1">
+      <x:c r="A8" s="254" t="str">
+        <x:v>RPT-4001</x:v>
+      </x:c>
+      <x:c r="B8" s="254" t="str">
+        <x:v>日報</x:v>
+      </x:c>
+      <x:c r="C8" s="254" t="str">
+        <x:v>当日日報あり</x:v>
+      </x:c>
+      <x:c r="D8" s="254" t="n">
+        <x:v>409</x:v>
+      </x:c>
+      <x:c r="E8" s="254" t="str">
+        <x:v>18／31B_ErrorMessage対応参照</x:v>
+      </x:c>
+      <x:c r="F8" s="254" t="str">
+        <x:v>WARN</x:v>
+      </x:c>
+      <x:c r="G8" s="254" t="str">
+        <x:v>不可</x:v>
+      </x:c>
+      <x:c r="H8" s="254" t="str"/>
+    </x:row>
+    <x:row r="9" ht="42" customHeight="1">
+      <x:c r="A9" s="253" t="str">
+        <x:v>RPT-4002</x:v>
+      </x:c>
+      <x:c r="B9" s="253" t="str">
+        <x:v>日報</x:v>
+      </x:c>
+      <x:c r="C9" s="253" t="str">
+        <x:v>変更不可</x:v>
+      </x:c>
+      <x:c r="D9" s="253" t="n">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="E9" s="33" t="str">
-        <x:v>入力または処理内容を確認してください。</x:v>
-      </x:c>
-      <x:c r="F9" s="33" t="str">
+      <x:c r="E9" s="253" t="str">
+        <x:v>18／31B_ErrorMessage対応参照</x:v>
+      </x:c>
+      <x:c r="F9" s="253" t="str">
         <x:v>WARN</x:v>
       </x:c>
-      <x:c r="G9" s="33" t="str">
-        <x:v>不可</x:v>
-      </x:c>
-      <x:c r="H9" s="33"/>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="33" t="str">
-        <x:v>COMMON-4040</x:v>
-      </x:c>
-      <x:c r="B10" s="33" t="str">
-        <x:v>Data</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="str">
-        <x:v>Data存在しない</x:v>
-      </x:c>
-      <x:c r="D10" s="33" t="n">
-        <x:v>404</x:v>
-      </x:c>
-      <x:c r="E10" s="33" t="str">
-        <x:v>入力または処理内容を確認してください。</x:v>
-      </x:c>
-      <x:c r="F10" s="33" t="str">
+      <x:c r="G9" s="253" t="str">
+        <x:v>不可</x:v>
+      </x:c>
+      <x:c r="H9" s="253" t="str"/>
+    </x:row>
+    <x:row r="10" ht="57" customHeight="1">
+      <x:c r="A10" s="254" t="str">
+        <x:v>RPT-4003</x:v>
+      </x:c>
+      <x:c r="B10" s="254" t="str">
+        <x:v>日報</x:v>
+      </x:c>
+      <x:c r="C10" s="254" t="str">
+        <x:v>関連Task不正</x:v>
+      </x:c>
+      <x:c r="D10" s="254" t="n">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="E10" s="254" t="str">
+        <x:v>18／31B_ErrorMessage対応参照</x:v>
+      </x:c>
+      <x:c r="F10" s="254" t="str">
         <x:v>WARN</x:v>
       </x:c>
-      <x:c r="G10" s="33" t="str">
-        <x:v>不可</x:v>
-      </x:c>
-      <x:c r="H10" s="33"/>
+      <x:c r="G10" s="254" t="str">
+        <x:v>不可</x:v>
+      </x:c>
+      <x:c r="H10" s="254" t="str">
+        <x:v>Task不存在、削除済、Project不一致、重複指定を含む</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="33" t="str">
-        <x:v>COMMON-4090</x:v>
-      </x:c>
-      <x:c r="B11" s="33" t="str">
-        <x:v>競合</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="str">
-        <x:v>並行更新Conflict</x:v>
-      </x:c>
-      <x:c r="D11" s="33" t="n">
-        <x:v>409</x:v>
-      </x:c>
-      <x:c r="E11" s="33" t="str">
-        <x:v>入力または処理内容を確認してください。</x:v>
-      </x:c>
-      <x:c r="F11" s="33" t="str">
-        <x:v>WARN</x:v>
-      </x:c>
-      <x:c r="G11" s="33" t="str">
-        <x:v>不可</x:v>
-      </x:c>
-      <x:c r="H11" s="33"/>
+      <x:c r="A11"/>
+      <x:c r="B11"/>
+      <x:c r="C11"/>
+      <x:c r="D11"/>
+      <x:c r="E11"/>
+      <x:c r="F11"/>
+      <x:c r="G11"/>
+      <x:c r="H11"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="33" t="str">
-        <x:v>COMMON-5000</x:v>
-      </x:c>
-      <x:c r="B12" s="33" t="str">
-        <x:v>System</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="str">
-        <x:v>System error</x:v>
-      </x:c>
-      <x:c r="D12" s="33" t="n">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="E12" s="33" t="str">
-        <x:v>入力または処理内容を確認してください。</x:v>
-      </x:c>
-      <x:c r="F12" s="33" t="str">
-        <x:v>ERROR</x:v>
-      </x:c>
-      <x:c r="G12" s="33" t="str">
-        <x:v>可</x:v>
-      </x:c>
-      <x:c r="H12" s="33"/>
+      <x:c r="A12"/>
+      <x:c r="B12"/>
+      <x:c r="C12"/>
+      <x:c r="D12"/>
+      <x:c r="E12"/>
+      <x:c r="F12"/>
+      <x:c r="G12"/>
+      <x:c r="H12"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="33" t="str">
-        <x:v>RPT-4001</x:v>
-      </x:c>
-      <x:c r="B13" s="33" t="str">
-        <x:v>日報</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="str">
-        <x:v>当日日報あり</x:v>
-      </x:c>
-      <x:c r="D13" s="33" t="n">
-        <x:v>409</x:v>
-      </x:c>
-      <x:c r="E13" s="33" t="str">
-        <x:v>入力または処理内容を確認してください。</x:v>
-      </x:c>
-      <x:c r="F13" s="33" t="str">
-        <x:v>WARN</x:v>
-      </x:c>
-      <x:c r="G13" s="33" t="str">
-        <x:v>不可</x:v>
-      </x:c>
-      <x:c r="H13" s="33"/>
+      <x:c r="A13"/>
+      <x:c r="B13"/>
+      <x:c r="C13"/>
+      <x:c r="D13"/>
+      <x:c r="E13"/>
+      <x:c r="F13"/>
+      <x:c r="G13"/>
+      <x:c r="H13"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="33" t="str">
-        <x:v>RPT-4002</x:v>
-      </x:c>
-      <x:c r="B14" s="33" t="str">
-        <x:v>日報</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="str">
-        <x:v>変更不可</x:v>
-      </x:c>
-      <x:c r="D14" s="33" t="n">
-        <x:v>400</x:v>
-      </x:c>
-      <x:c r="E14" s="33" t="str">
-        <x:v>入力または処理内容を確認してください。</x:v>
-      </x:c>
-      <x:c r="F14" s="33" t="str">
-        <x:v>WARN</x:v>
-      </x:c>
-      <x:c r="G14" s="33" t="str">
-        <x:v>不可</x:v>
-      </x:c>
-      <x:c r="H14" s="33"/>
-    </x:row>
-    <x:row r="15">
+      <x:c r="A14"/>
+      <x:c r="B14"/>
+      <x:c r="C14"/>
+      <x:c r="D14"/>
+      <x:c r="E14"/>
+      <x:c r="F14"/>
+      <x:c r="G14"/>
+      <x:c r="H14"/>
+    </x:row>
+    <x:row r="15" ht="36" customHeight="1">
       <x:c r="A15"/>
       <x:c r="B15"/>
       <x:c r="C15"/>
@@ -3067,16 +3199,9 @@
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:H2"/>
-    <x:mergeCell ref="A3:B3"/>
-    <x:mergeCell ref="C3:D3"/>
-    <x:mergeCell ref="E3:F3"/>
-    <x:mergeCell ref="G3:H3"/>
-    <x:mergeCell ref="A4:B4"/>
-    <x:mergeCell ref="C4:D4"/>
-    <x:mergeCell ref="E4:F4"/>
-    <x:mergeCell ref="G4:H4"/>
-    <x:mergeCell ref="A6:H6"/>
+    <x:mergeCell ref="A1:H1"/>
+    <x:mergeCell ref="A3:H3"/>
+    <x:mergeCell ref="A5:H5"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -3087,19 +3212,19 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="72" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="72" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="48" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="42" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="24" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="34" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="90" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="48" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="26" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="34" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="44" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="30" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="30" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="68" t="str">
-        <x:v>API外部契約</x:v>
+        <x:v>API処理・権限概要</x:v>
       </x:c>
       <x:c r="B1" s="68"/>
       <x:c r="C1" s="68"/>
@@ -3107,8 +3232,6 @@
       <x:c r="E1" s="68"/>
       <x:c r="F1" s="68"/>
       <x:c r="G1" s="68"/>
-      <x:c r="H1" s="68"/>
-      <x:c r="I1" s="68"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="68"/>
@@ -3118,8 +3241,6 @@
       <x:c r="E2" s="68"/>
       <x:c r="F2" s="68"/>
       <x:c r="G2" s="68"/>
-      <x:c r="H2" s="68"/>
-      <x:c r="I2" s="68"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="62" t="str">
@@ -3129,35 +3250,31 @@
         <x:v>Company WorkHub</x:v>
       </x:c>
       <x:c r="C3" s="63"/>
-      <x:c r="D3" s="63"/>
-      <x:c r="E3" s="62" t="str">
-        <x:v>文書番号</x:v>
-      </x:c>
-      <x:c r="F3" s="63" t="str">
-        <x:v>CW-BD-API-RPT-CONTRACT</x:v>
-      </x:c>
+      <x:c r="D3" s="246" t="str">
+        <x:v>章ID</x:v>
+      </x:c>
+      <x:c r="E3" s="63" t="str">
+        <x:v>CW-BD-API-RPT-FLOW</x:v>
+      </x:c>
+      <x:c r="F3" s="63"/>
       <x:c r="G3" s="63"/>
-      <x:c r="H3" s="63"/>
-      <x:c r="I3" s="63"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="62" t="str">
         <x:v>版数</x:v>
       </x:c>
       <x:c r="B4" s="63" t="str">
-        <x:v>Ver.1.8</x:v>
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="C4" s="63"/>
-      <x:c r="D4" s="63"/>
-      <x:c r="E4" s="62" t="str">
+      <x:c r="D4" s="62" t="str">
         <x:v>改訂日</x:v>
       </x:c>
-      <x:c r="F4" s="63" t="str">
-        <x:v>2026-08-12</x:v>
-      </x:c>
+      <x:c r="E4" s="63" t="str">
+        <x:v>2026-09-24</x:v>
+      </x:c>
+      <x:c r="F4" s="63"/>
       <x:c r="G4" s="63"/>
-      <x:c r="H4" s="63"/>
-      <x:c r="I4" s="63"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="64"/>
@@ -3167,12 +3284,10 @@
       <x:c r="E5" s="64"/>
       <x:c r="F5" s="64"/>
       <x:c r="G5" s="64"/>
-      <x:c r="H5" s="64"/>
-      <x:c r="I5" s="64"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="65" t="str">
-        <x:v>1. 日報・通知 Request/Response・権限契約</x:v>
+        <x:v>1. API単位処理概要</x:v>
       </x:c>
       <x:c r="B6" s="65"/>
       <x:c r="C6" s="65"/>
@@ -3180,238 +3295,269 @@
       <x:c r="E6" s="65"/>
       <x:c r="F6" s="65"/>
       <x:c r="G6" s="65"/>
-      <x:c r="H6" s="65"/>
-      <x:c r="I6" s="65"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="66" t="str">
         <x:v>API ID</x:v>
       </x:c>
       <x:c r="B7" s="66" t="str">
-        <x:v>Request定義</x:v>
+        <x:v>機能</x:v>
       </x:c>
       <x:c r="C7" s="66" t="str">
-        <x:v>Response定義</x:v>
-      </x:c>
-      <x:c r="D7" s="66" t="str">
-        <x:v>Role</x:v>
+        <x:v>処理概要</x:v>
+      </x:c>
+      <x:c r="D7" s="255" t="str">
+        <x:v>認可参照</x:v>
       </x:c>
       <x:c r="E7" s="66" t="str">
-        <x:v>Data範囲</x:v>
+        <x:v>Transaction</x:v>
       </x:c>
       <x:c r="F7" s="66" t="str">
-        <x:v>参照・更新Table</x:v>
+        <x:v>Error Code</x:v>
       </x:c>
       <x:c r="G7" s="66" t="str">
-        <x:v>Transaction</x:v>
-      </x:c>
-      <x:c r="H7" s="66" t="str">
-        <x:v>Error Code</x:v>
-      </x:c>
-      <x:c r="I7" s="66" t="str">
-        <x:v>利用画面</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
+        <x:v>Log</x:v>
+      </x:c>
+      <x:c r="H7" s="203" t="str">
+        <x:v>関連Table</x:v>
+      </x:c>
+      <x:c r="I7" s="203" t="str">
+        <x:v>利用元・補足</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="166" customHeight="1">
       <x:c r="A8" s="67" t="str">
         <x:v>API-RPT-001</x:v>
       </x:c>
       <x:c r="B8" s="67" t="str">
-        <x:v>query: employeeId,departmentId,projectId,dateFrom,dateTo,hasIssue,missing,page,size,sort</x:v>
+        <x:v>日報検索</x:v>
       </x:c>
       <x:c r="C8" s="67" t="str">
-        <x:v>Page&lt;DailyReportSummary&gt;</x:v>
+        <x:v>1) 02の対応Permission/Data Scopeを判定。2) 23_API項目定義に従い入力を検証。3) daily_reports,employees,projectsを参照。4) 業務Dataの更新なし。5) 23_API項目定義の正常Responseを返す。</x:v>
       </x:c>
       <x:c r="D8" s="67" t="str">
-        <x:v>権限別</x:v>
+        <x:v>02／13_API権限対応 API-RPT-001
+Permission: PERM-RPT-SELF / PERM-RPT-TEAM
+Data Scope: DS-RPT-001</x:v>
       </x:c>
       <x:c r="E8" s="67" t="str">
-        <x:v>ADMIN=全社, PM=担当PJ, EMP=本人</x:v>
+        <x:v>参照</x:v>
       </x:c>
       <x:c r="F8" s="67" t="str">
+        <x:v>COMMON-4000/AUTH-4006</x:v>
+      </x:c>
+      <x:c r="G8" s="67" t="str">
+        <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
+      </x:c>
+      <x:c r="H8" s="241" t="str">
         <x:v>daily_reports,employees,projects</x:v>
       </x:c>
-      <x:c r="G8" s="67" t="str">
-        <x:v>参照</x:v>
-      </x:c>
-      <x:c r="H8" s="67" t="str">
-        <x:v>COMMON-4000/AUTH-4006</x:v>
-      </x:c>
-      <x:c r="I8" s="67" t="str">
+      <x:c r="I8" s="241" t="str">
         <x:v>SCR-019, SCR-021</x:v>
       </x:c>
+      <x:c r="J8" s="241"/>
+      <x:c r="K8" s="241"/>
+      <x:c r="L8" s="241"/>
     </x:row>
     <x:row r="9" ht="30" customHeight="1">
       <x:c r="A9" s="67" t="str">
         <x:v>API-RPT-002</x:v>
       </x:c>
       <x:c r="B9" s="67" t="str">
-        <x:v>path: id Long</x:v>
+        <x:v>日報詳細</x:v>
       </x:c>
       <x:c r="C9" s="67" t="str">
-        <x:v>DailyReportDetail + tasks[]</x:v>
+        <x:v>1) 02の対応Permission/Data Scopeを判定。2) 23_API項目定義に従い入力を検証。3) daily_reports,daily_report_tasks,tasksを参照。4) 業務Dataの更新なし。5) 23_API項目定義の正常Responseを返す。</x:v>
       </x:c>
       <x:c r="D9" s="67" t="str">
-        <x:v>権限別</x:v>
+        <x:v>02／13_API権限対応 API-RPT-002
+Permission: PERM-RPT-SELF / PERM-RPT-TEAM
+Data Scope: DS-RPT-002</x:v>
       </x:c>
       <x:c r="E9" s="67" t="str">
-        <x:v>ADMIN=全社, PM=担当PJ, EMP=本人</x:v>
+        <x:v>参照</x:v>
       </x:c>
       <x:c r="F9" s="67" t="str">
+        <x:v>COMMON-4040/AUTH-4006</x:v>
+      </x:c>
+      <x:c r="G9" s="67" t="str">
+        <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
+      </x:c>
+      <x:c r="H9" s="203" t="str">
         <x:v>daily_reports,daily_report_tasks,tasks</x:v>
       </x:c>
-      <x:c r="G9" s="67" t="str">
-        <x:v>参照</x:v>
-      </x:c>
-      <x:c r="H9" s="67" t="str">
-        <x:v>COMMON-4040/AUTH-4006</x:v>
-      </x:c>
-      <x:c r="I9" s="67" t="str">
+      <x:c r="I9" s="203" t="str">
         <x:v>SCR-019, SCR-020, SCR-021</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="30" customHeight="1">
+    <x:row r="10" ht="222" customHeight="1">
       <x:c r="A10" s="67" t="str">
         <x:v>API-RPT-003</x:v>
       </x:c>
       <x:c r="B10" s="67" t="str">
-        <x:v>body: reportDate,projectId,completedWork,plannedWork,issues,workingHours,taskIds[]; header: X-Idempotency-Key</x:v>
+        <x:v>日報登録</x:v>
       </x:c>
       <x:c r="C10" s="67" t="str">
-        <x:v>id,version</x:v>
+        <x:v>1) 認証・Permission・Data範囲、Request項目、日報編集期限を確認。2) 登録社員・PJ・報告日の重複とMember条件を確認。3) taskIds重複なし・全件存在・未削除・request.body.projectIdと同一PJを検証。不一致はRPT-4003。4) TX-006内で対象状態・競合を再確認しdaily_reports/daily_report_tasksと成功監査Logを更新。失敗は全Rollback。5) Commit成功後のみid/versionを返却。
+Commit前に社員行を排他してBR-RPT-004の24時間合計を確認。報告日当日の在籍/参加履歴・PJ期間を確認。休日作業登録可。削除済日報はUniqueと集計から除外。</x:v>
       </x:c>
       <x:c r="D10" s="67" t="str">
-        <x:v>全員</x:v>
+        <x:v>02／13_API権限対応 API-RPT-003
+Permission: PERM-RPT-SELF
+Data Scope: DS-RPT-003</x:v>
       </x:c>
       <x:c r="E10" s="67" t="str">
-        <x:v>本人; 当該PJ Member</x:v>
+        <x:v>TX-006</x:v>
       </x:c>
       <x:c r="F10" s="67" t="str">
+        <x:v>RPT-4001, RPT-4002,COMMON-4090, RPT-4003
+COMMON-4000</x:v>
+      </x:c>
+      <x:c r="G10" s="67" t="str">
+        <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
+      </x:c>
+      <x:c r="H10" s="241" t="str">
         <x:v>daily_reports,daily_report_tasks,operation_logs</x:v>
       </x:c>
-      <x:c r="G10" s="67" t="str">
-        <x:v>TX-006</x:v>
-      </x:c>
-      <x:c r="H10" s="67" t="str">
-        <x:v>RPT-4001, RPT-4002,COMMON-4090</x:v>
-      </x:c>
-      <x:c r="I10" s="67" t="str">
+      <x:c r="I10" s="241" t="str">
         <x:v>SCR-020</x:v>
       </x:c>
-    </x:row>
-    <x:row r="11" ht="30" customHeight="1">
+      <x:c r="J10" s="241"/>
+      <x:c r="K10" s="241"/>
+      <x:c r="L10" s="241"/>
+    </x:row>
+    <x:row r="11" ht="222" customHeight="1">
       <x:c r="A11" s="67" t="str">
         <x:v>API-RPT-004</x:v>
       </x:c>
       <x:c r="B11" s="67" t="str">
-        <x:v>path: id; body: completedWork,plannedWork,issues,workingHours,taskIds[],version</x:v>
+        <x:v>日報更新</x:v>
       </x:c>
       <x:c r="C11" s="67" t="str">
-        <x:v>id,version</x:v>
+        <x:v>1) 認証・Permission・Data範囲、Request項目、日報編集期限を確認。2) 対象日報の存在とversionを確認。3) taskIds重複なし・全件存在・未削除・既存日報のproject_idと同一PJを検証。不一致はRPT-4003。4) TX-023内で対象状態・競合を再確認しdaily_reports/daily_report_tasksと成功監査Logを更新。失敗は全Rollback。5) Commit成功後のみid/versionを返却。
+Commit前に社員行を排他してBR-RPT-004の24時間合計を確認。報告日当日の在籍/参加履歴・PJ期間を確認。休日作業登録可。削除済日報はUniqueと集計から除外。</x:v>
       </x:c>
       <x:c r="D11" s="67" t="str">
-        <x:v>本人/管理者</x:v>
+        <x:v>02／13_API権限対応 API-RPT-004
+Permission: PERM-RPT-SELF
+Data Scope: DS-RPT-004</x:v>
       </x:c>
       <x:c r="E11" s="67" t="str">
-        <x:v>本人=当日・前営業日, ADMIN=全期間</x:v>
+        <x:v>TX-023</x:v>
       </x:c>
       <x:c r="F11" s="67" t="str">
+        <x:v>RPT-4002,COMMON-4040, COMMON-4090, RPT-4003
+COMMON-4000</x:v>
+      </x:c>
+      <x:c r="G11" s="67" t="str">
+        <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
+      </x:c>
+      <x:c r="H11" s="241" t="str">
         <x:v>daily_reports,daily_report_tasks,operation_logs</x:v>
       </x:c>
-      <x:c r="G11" s="67" t="str">
-        <x:v>TX-023</x:v>
-      </x:c>
-      <x:c r="H11" s="67" t="str">
-        <x:v>RPT-4002,COMMON-4040, COMMON-4090</x:v>
-      </x:c>
-      <x:c r="I11" s="67" t="str">
+      <x:c r="I11" s="241" t="str">
         <x:v>SCR-020</x:v>
       </x:c>
-    </x:row>
-    <x:row r="12" ht="30" customHeight="1">
+      <x:c r="J11" s="241"/>
+      <x:c r="K11" s="241"/>
+      <x:c r="L11" s="241"/>
+    </x:row>
+    <x:row r="12" ht="96" customHeight="1">
       <x:c r="A12" s="67" t="str">
         <x:v>API-RPT-005</x:v>
       </x:c>
       <x:c r="B12" s="67" t="str">
-        <x:v>path: id; query: version</x:v>
+        <x:v>日報削除</x:v>
       </x:c>
       <x:c r="C12" s="67" t="str">
-        <x:v>204 No Content</x:v>
+        <x:v>本人/ADMIN・編集期限・存在/version確認。TX-023で社員行排他、日報deleted=true、関連Task紐付けは履歴保持して通常参照除外、監査をCommit。204本文なし。後の同鍵登録は新IDで可。削除済IDは404。失敗全Rollback。</x:v>
       </x:c>
       <x:c r="D12" s="67" t="str">
-        <x:v>本人/管理者</x:v>
+        <x:v>02／13_API権限対応 API-RPT-005
+Permission: PERM-RPT-SELF
+Data Scope: DS-RPT-005</x:v>
       </x:c>
       <x:c r="E12" s="67" t="str">
-        <x:v>本人=当日・前営業日, ADMIN=全期間</x:v>
+        <x:v>TX-023</x:v>
       </x:c>
       <x:c r="F12" s="67" t="str">
+        <x:v>RPT-4002, COMMON-4040, COMMON-4090</x:v>
+      </x:c>
+      <x:c r="G12" s="67" t="str">
+        <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
+      </x:c>
+      <x:c r="H12" s="241" t="str">
         <x:v>daily_reports,daily_report_tasks,operation_logs</x:v>
       </x:c>
-      <x:c r="G12" s="67" t="str">
-        <x:v>TX-023</x:v>
-      </x:c>
-      <x:c r="H12" s="67" t="str">
-        <x:v>RPT-4002,COMMON-4090</x:v>
-      </x:c>
-      <x:c r="I12" s="67" t="str">
+      <x:c r="I12" s="241" t="str">
         <x:v>SCR-019, SCR-020</x:v>
       </x:c>
-    </x:row>
-    <x:row r="13" ht="30" customHeight="1">
+      <x:c r="J12" s="241"/>
+      <x:c r="K12" s="241"/>
+      <x:c r="L12" s="241"/>
+    </x:row>
+    <x:row r="13" ht="124" customHeight="1">
       <x:c r="A13" s="67" t="str">
         <x:v>API-RPT-006</x:v>
       </x:c>
       <x:c r="B13" s="67" t="str">
-        <x:v>query: date,projectId,page,size</x:v>
+        <x:v>未提出者検索</x:v>
       </x:c>
       <x:c r="C13" s="67" t="str">
-        <x:v>Page&lt;EmployeeSummary&gt;</x:v>
+        <x:v>ADMIN全社/PM担当PJに限定。date省略=当日JST、未来不可。任意projectId/employeeId/departmentIdを現在所属でAND絞込。16／28 BR-RPT-005の社員×PJ×指定日を抽出。既存未削除日報を除外し社員番号→PJ番号昇順。idを捏造せず23のMissingReport行をPage返却。休日/0件は空Page。</x:v>
       </x:c>
       <x:c r="D13" s="67" t="str">
-        <x:v>管理者/担当PM</x:v>
+        <x:v>02／13_API権限対応 API-RPT-006
+Permission: PERM-RPT-TEAM
+Data Scope: DS-RPT-006</x:v>
       </x:c>
       <x:c r="E13" s="67" t="str">
-        <x:v>ADMIN=全社, PM=担当PJ</x:v>
+        <x:v>参照</x:v>
       </x:c>
       <x:c r="F13" s="67" t="str">
+        <x:v>COMMON-4000, AUTH-4006</x:v>
+      </x:c>
+      <x:c r="G13" s="67" t="str">
+        <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
+      </x:c>
+      <x:c r="H13" s="241" t="str">
         <x:v>employees,project_members,daily_reports,business_holidays</x:v>
       </x:c>
-      <x:c r="G13" s="67" t="str">
-        <x:v>参照</x:v>
-      </x:c>
-      <x:c r="H13" s="67" t="str">
-        <x:v>COMMON-4000</x:v>
-      </x:c>
-      <x:c r="I13" s="67" t="str">
+      <x:c r="I13" s="241" t="str">
         <x:v>SCR-021</x:v>
       </x:c>
+      <x:c r="J13" s="241"/>
+      <x:c r="K13" s="241"/>
+      <x:c r="L13" s="241"/>
     </x:row>
     <x:row r="14" ht="30" customHeight="1">
       <x:c r="A14" s="67" t="str">
         <x:v>API-NTF-001</x:v>
       </x:c>
       <x:c r="B14" s="67" t="str">
-        <x:v>query: read,type,page,size,sort</x:v>
+        <x:v>通知一覧</x:v>
       </x:c>
       <x:c r="C14" s="67" t="str">
-        <x:v>Page&lt;Notification&gt;</x:v>
+        <x:v>1) 02の対応Permission/Data Scopeを判定。2) 23_API項目定義に従い入力を検証。3) notificationsを参照。4) 業務Dataの更新なし。5) 23_API項目定義の正常Responseを返す。</x:v>
       </x:c>
       <x:c r="D14" s="67" t="str">
-        <x:v>全員</x:v>
+        <x:v>02／13_API権限対応 API-NTF-001
+Permission: -（認証/本人共通）
+Data Scope: DS-NTF-001</x:v>
       </x:c>
       <x:c r="E14" s="67" t="str">
-        <x:v>本人通知のみ</x:v>
+        <x:v>参照</x:v>
       </x:c>
       <x:c r="F14" s="67" t="str">
+        <x:v>COMMON-4000</x:v>
+      </x:c>
+      <x:c r="G14" s="67" t="str">
+        <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
+      </x:c>
+      <x:c r="H14" s="203" t="str">
         <x:v>notifications</x:v>
       </x:c>
-      <x:c r="G14" s="67" t="str">
-        <x:v>参照</x:v>
-      </x:c>
-      <x:c r="H14" s="67" t="str">
-        <x:v>COMMON-4000</x:v>
-      </x:c>
-      <x:c r="I14" s="67" t="str">
+      <x:c r="I14" s="203" t="str">
         <x:v>SCR-022</x:v>
       </x:c>
     </x:row>
@@ -3420,460 +3566,77 @@
         <x:v>API-NTF-002</x:v>
       </x:c>
       <x:c r="B15" s="67" t="str">
-        <x:v>なし</x:v>
+        <x:v>未読件数</x:v>
       </x:c>
       <x:c r="C15" s="67" t="str">
-        <x:v>count Integer</x:v>
+        <x:v>1) 02の対応Permission/Data Scopeを判定。2) 23_API項目定義に従い入力を検証。3) notificationsを参照。4) 業務Dataの更新なし。5) 23_API項目定義の正常Responseを返す。</x:v>
       </x:c>
       <x:c r="D15" s="67" t="str">
-        <x:v>全員</x:v>
+        <x:v>02／13_API権限対応 API-NTF-002
+Permission: -（認証/本人共通）
+Data Scope: DS-NTF-002</x:v>
       </x:c>
       <x:c r="E15" s="67" t="str">
-        <x:v>本人通知のみ</x:v>
+        <x:v>参照</x:v>
       </x:c>
       <x:c r="F15" s="67" t="str">
+        <x:v>COMMON-5000</x:v>
+      </x:c>
+      <x:c r="G15" s="67" t="str">
+        <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
+      </x:c>
+      <x:c r="H15" s="203" t="str">
         <x:v>notifications</x:v>
       </x:c>
-      <x:c r="G15" s="67" t="str">
-        <x:v>参照</x:v>
-      </x:c>
-      <x:c r="H15" s="67" t="str">
-        <x:v>COMMON-5000</x:v>
-      </x:c>
-      <x:c r="I15" s="67" t="str">
-        <x:v>共通Header/SCR-002</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="30" customHeight="1">
+      <x:c r="I15" s="203" t="str">
+        <x:v>共通Header</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="91" customHeight="1">
       <x:c r="A16" s="67" t="str">
         <x:v>API-NTF-003</x:v>
       </x:c>
       <x:c r="B16" s="67" t="str">
-        <x:v>path: id</x:v>
+        <x:v>既読化</x:v>
       </x:c>
       <x:c r="C16" s="67" t="str">
-        <x:v>id,isRead,readAt</x:v>
+        <x:v>1) 02の対応Permission/Data Scopeを判定。2) 23_API項目定義に従い入力を検証。3) notificationsを参照/更新。4) TX-024の境界でCommit/Rollback。5) 23_API項目定義の正常Responseを返す。</x:v>
       </x:c>
       <x:c r="D16" s="67" t="str">
-        <x:v>本人</x:v>
+        <x:v>02／13_API権限対応 API-NTF-003
+Permission: -（認証/本人共通）
+Data Scope: DS-NTF-003</x:v>
       </x:c>
       <x:c r="E16" s="67" t="str">
-        <x:v>受信者本人</x:v>
+        <x:v>TX-024</x:v>
       </x:c>
       <x:c r="F16" s="67" t="str">
+        <x:v>COMMON-4040/AUTH-4006</x:v>
+      </x:c>
+      <x:c r="G16" s="67" t="str">
+        <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
+      </x:c>
+      <x:c r="H16" s="203" t="str">
         <x:v>notifications</x:v>
       </x:c>
-      <x:c r="G16" s="67" t="str">
-        <x:v>TX-024</x:v>
-      </x:c>
-      <x:c r="H16" s="67" t="str">
-        <x:v>COMMON-4040/AUTH-4006</x:v>
-      </x:c>
-      <x:c r="I16" s="67" t="str">
+      <x:c r="I16" s="203" t="str">
         <x:v>SCR-022</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="30" customHeight="1">
+    <x:row r="17" ht="104" customHeight="1">
       <x:c r="A17" s="67" t="str">
         <x:v>API-NTF-004</x:v>
       </x:c>
       <x:c r="B17" s="67" t="str">
-        <x:v>body: before DateTime?</x:v>
+        <x:v>全件既読</x:v>
       </x:c>
       <x:c r="C17" s="67" t="str">
-        <x:v>updatedCount</x:v>
+        <x:v>1) 02の対応Permission/Data Scopeを判定。2) 23_API項目定義に従い入力を検証。3) notificationsを参照/更新。4) TX-024の境界でCommit/Rollback。5) 23_API項目定義の正常Responseを返す。</x:v>
       </x:c>
       <x:c r="D17" s="67" t="str">
-        <x:v>本人</x:v>
-      </x:c>
-      <x:c r="E17" s="67" t="str">
-        <x:v>受信者本人</x:v>
-      </x:c>
-      <x:c r="F17" s="67" t="str">
-        <x:v>notifications</x:v>
-      </x:c>
-      <x:c r="G17" s="67" t="str">
-        <x:v>TX-024</x:v>
-      </x:c>
-      <x:c r="H17" s="67" t="str">
-        <x:v>COMMON-4000</x:v>
-      </x:c>
-      <x:c r="I17" s="67" t="str">
-        <x:v>SCR-022</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="64"/>
-      <x:c r="B18" s="64"/>
-      <x:c r="C18" s="64"/>
-      <x:c r="D18" s="64"/>
-      <x:c r="E18" s="64"/>
-      <x:c r="F18" s="64"/>
-      <x:c r="G18" s="64"/>
-      <x:c r="H18" s="64"/>
-      <x:c r="I18" s="64"/>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19"/>
-      <x:c r="B19"/>
-      <x:c r="C19"/>
-      <x:c r="D19"/>
-      <x:c r="E19"/>
-      <x:c r="F19"/>
-      <x:c r="G19"/>
-      <x:c r="H19"/>
-      <x:c r="I19"/>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="91"/>
-      <x:c r="B20" s="92"/>
-      <x:c r="C20" s="92"/>
-      <x:c r="D20" s="92"/>
-      <x:c r="E20" s="92"/>
-      <x:c r="F20" s="92"/>
-      <x:c r="G20" s="92"/>
-      <x:c r="H20" s="92"/>
-      <x:c r="I20" s="93"/>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:I2"/>
-    <x:mergeCell ref="A6:I6"/>
-    <x:mergeCell ref="A19:I20"/>
-  </x:mergeCells>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="90" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="48" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="26" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="34" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="44" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="68" t="str">
-        <x:v>API処理・権限概要</x:v>
-      </x:c>
-      <x:c r="B1" s="68"/>
-      <x:c r="C1" s="68"/>
-      <x:c r="D1" s="68"/>
-      <x:c r="E1" s="68"/>
-      <x:c r="F1" s="68"/>
-      <x:c r="G1" s="68"/>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="68"/>
-      <x:c r="B2" s="68"/>
-      <x:c r="C2" s="68"/>
-      <x:c r="D2" s="68"/>
-      <x:c r="E2" s="68"/>
-      <x:c r="F2" s="68"/>
-      <x:c r="G2" s="68"/>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="62" t="str">
-        <x:v>システム名</x:v>
-      </x:c>
-      <x:c r="B3" s="63" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="C3" s="63"/>
-      <x:c r="D3" s="62" t="str">
-        <x:v>文書番号</x:v>
-      </x:c>
-      <x:c r="E3" s="63" t="str">
-        <x:v>CW-BD-API-RPT-FLOW</x:v>
-      </x:c>
-      <x:c r="F3" s="63"/>
-      <x:c r="G3" s="63"/>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="62" t="str">
-        <x:v>版数</x:v>
-      </x:c>
-      <x:c r="B4" s="63" t="str">
-        <x:v>Ver.1.8</x:v>
-      </x:c>
-      <x:c r="C4" s="63"/>
-      <x:c r="D4" s="62" t="str">
-        <x:v>改訂日</x:v>
-      </x:c>
-      <x:c r="E4" s="63" t="str">
-        <x:v>2026-08-12</x:v>
-      </x:c>
-      <x:c r="F4" s="63"/>
-      <x:c r="G4" s="63"/>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="64"/>
-      <x:c r="B5" s="64"/>
-      <x:c r="C5" s="64"/>
-      <x:c r="D5" s="64"/>
-      <x:c r="E5" s="64"/>
-      <x:c r="F5" s="64"/>
-      <x:c r="G5" s="64"/>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="65" t="str">
-        <x:v>1. API単位処理概要</x:v>
-      </x:c>
-      <x:c r="B6" s="65"/>
-      <x:c r="C6" s="65"/>
-      <x:c r="D6" s="65"/>
-      <x:c r="E6" s="65"/>
-      <x:c r="F6" s="65"/>
-      <x:c r="G6" s="65"/>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="66" t="str">
-        <x:v>API ID</x:v>
-      </x:c>
-      <x:c r="B7" s="66" t="str">
-        <x:v>機能</x:v>
-      </x:c>
-      <x:c r="C7" s="66" t="str">
-        <x:v>処理概要</x:v>
-      </x:c>
-      <x:c r="D7" s="66" t="str">
-        <x:v>Data範囲</x:v>
-      </x:c>
-      <x:c r="E7" s="66" t="str">
-        <x:v>Transaction</x:v>
-      </x:c>
-      <x:c r="F7" s="66" t="str">
-        <x:v>Error Code</x:v>
-      </x:c>
-      <x:c r="G7" s="66" t="str">
-        <x:v>Log</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="67" t="str">
-        <x:v>API-RPT-001</x:v>
-      </x:c>
-      <x:c r="B8" s="67" t="str">
-        <x:v>日報検索</x:v>
-      </x:c>
-      <x:c r="C8" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) query: employeeId,departmentId,projectId,dateFrom,dateTo,hasIssue,missing,page,size,sortを型・必須・桁・業務Ruleで検証。3) daily_reports,employees,projectsを参照/更新。4) 参照の境界でCommit/Rollback。5) Page&lt;DailyReportSummary&gt;を共通Response形式で返却。</x:v>
-      </x:c>
-      <x:c r="D8" s="67" t="str">
-        <x:v>ADMIN=全社, PM=担当PJ, EMP=本人</x:v>
-      </x:c>
-      <x:c r="E8" s="67" t="str">
-        <x:v>参照</x:v>
-      </x:c>
-      <x:c r="F8" s="67" t="str">
-        <x:v>COMMON-4000/AUTH-4006</x:v>
-      </x:c>
-      <x:c r="G8" s="67" t="str">
-        <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="67" t="str">
-        <x:v>API-RPT-002</x:v>
-      </x:c>
-      <x:c r="B9" s="67" t="str">
-        <x:v>日報詳細</x:v>
-      </x:c>
-      <x:c r="C9" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) path: id Longを型・必須・桁・業務Ruleで検証。3) daily_reports,daily_report_tasks,tasksを参照/更新。4) 参照の境界でCommit/Rollback。5) DailyReportDetail + tasks[]を共通Response形式で返却。</x:v>
-      </x:c>
-      <x:c r="D9" s="67" t="str">
-        <x:v>ADMIN=全社, PM=担当PJ, EMP=本人</x:v>
-      </x:c>
-      <x:c r="E9" s="67" t="str">
-        <x:v>参照</x:v>
-      </x:c>
-      <x:c r="F9" s="67" t="str">
-        <x:v>COMMON-4040/AUTH-4006</x:v>
-      </x:c>
-      <x:c r="G9" s="67" t="str">
-        <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="67" t="str">
-        <x:v>API-RPT-003</x:v>
-      </x:c>
-      <x:c r="B10" s="67" t="str">
-        <x:v>日報登録</x:v>
-      </x:c>
-      <x:c r="C10" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) body: reportDate,projectId,completedWork,plannedWork,issues,workingHours,taskIds[]; header: X-Idempotency-Keyを型・必須・桁・業務Ruleで検証。3) daily_reports,daily_report_tasks,operation_logsを参照/更新。4) TX-006の境界でCommit/Rollback。5) id,versionを共通Response形式で返却。</x:v>
-      </x:c>
-      <x:c r="D10" s="67" t="str">
-        <x:v>本人; 当該PJ Member</x:v>
-      </x:c>
-      <x:c r="E10" s="67" t="str">
-        <x:v>TX-006</x:v>
-      </x:c>
-      <x:c r="F10" s="67" t="str">
-        <x:v>RPT-4001, RPT-4002,COMMON-4090</x:v>
-      </x:c>
-      <x:c r="G10" s="67" t="str">
-        <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="30" customHeight="1">
-      <x:c r="A11" s="67" t="str">
-        <x:v>API-RPT-004</x:v>
-      </x:c>
-      <x:c r="B11" s="67" t="str">
-        <x:v>日報更新</x:v>
-      </x:c>
-      <x:c r="C11" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) path: id; body: completedWork,plannedWork,issues,workingHours,taskIds[],versionを型・必須・桁・業務Ruleで検証。3) daily_reports,daily_report_tasks,operation_logsを参照/更新。4) TX-RPT-UPDATEの境界でCommit/Rollback。5) id,versionを共通Response形式で返却。</x:v>
-      </x:c>
-      <x:c r="D11" s="67" t="str">
-        <x:v>本人=当日・前営業日, ADMIN=全期間</x:v>
-      </x:c>
-      <x:c r="E11" s="67" t="str">
-        <x:v>TX-023</x:v>
-      </x:c>
-      <x:c r="F11" s="67" t="str">
-        <x:v>RPT-4002,COMMON-4040, COMMON-4090</x:v>
-      </x:c>
-      <x:c r="G11" s="67" t="str">
-        <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="30" customHeight="1">
-      <x:c r="A12" s="67" t="str">
-        <x:v>API-RPT-005</x:v>
-      </x:c>
-      <x:c r="B12" s="67" t="str">
-        <x:v>日報削除</x:v>
-      </x:c>
-      <x:c r="C12" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) path: id; query: versionを型・必須・桁・業務Ruleで検証。3) daily_reports,daily_report_tasks,operation_logsを参照/更新。4) TX-RPT-DELETEの境界でCommit/Rollback。5) 204 No Contentを共通Response形式で返却。</x:v>
-      </x:c>
-      <x:c r="D12" s="67" t="str">
-        <x:v>本人=当日・前営業日, ADMIN=全期間</x:v>
-      </x:c>
-      <x:c r="E12" s="67" t="str">
-        <x:v>TX-023</x:v>
-      </x:c>
-      <x:c r="F12" s="67" t="str">
-        <x:v>RPT-4002,COMMON-4090</x:v>
-      </x:c>
-      <x:c r="G12" s="67" t="str">
-        <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="30" customHeight="1">
-      <x:c r="A13" s="67" t="str">
-        <x:v>API-RPT-006</x:v>
-      </x:c>
-      <x:c r="B13" s="67" t="str">
-        <x:v>未提出者検索</x:v>
-      </x:c>
-      <x:c r="C13" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) query: date,projectId,page,sizeを型・必須・桁・業務Ruleで検証。3) employees,project_members,daily_reports,business_holidaysを参照/更新。4) 参照の境界でCommit/Rollback。5) Page&lt;EmployeeSummary&gt;を共通Response形式で返却。</x:v>
-      </x:c>
-      <x:c r="D13" s="67" t="str">
-        <x:v>ADMIN=全社, PM=担当PJ</x:v>
-      </x:c>
-      <x:c r="E13" s="67" t="str">
-        <x:v>参照</x:v>
-      </x:c>
-      <x:c r="F13" s="67" t="str">
-        <x:v>COMMON-4000</x:v>
-      </x:c>
-      <x:c r="G13" s="67" t="str">
-        <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="30" customHeight="1">
-      <x:c r="A14" s="67" t="str">
-        <x:v>API-NTF-001</x:v>
-      </x:c>
-      <x:c r="B14" s="67" t="str">
-        <x:v>通知一覧</x:v>
-      </x:c>
-      <x:c r="C14" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) query: read,type,page,size,sortを型・必須・桁・業務Ruleで検証。3) notificationsを参照/更新。4) 参照の境界でCommit/Rollback。5) Page&lt;Notification&gt;を共通Response形式で返却。</x:v>
-      </x:c>
-      <x:c r="D14" s="67" t="str">
-        <x:v>本人通知のみ</x:v>
-      </x:c>
-      <x:c r="E14" s="67" t="str">
-        <x:v>参照</x:v>
-      </x:c>
-      <x:c r="F14" s="67" t="str">
-        <x:v>COMMON-4000</x:v>
-      </x:c>
-      <x:c r="G14" s="67" t="str">
-        <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="30" customHeight="1">
-      <x:c r="A15" s="67" t="str">
-        <x:v>API-NTF-002</x:v>
-      </x:c>
-      <x:c r="B15" s="67" t="str">
-        <x:v>未読件数</x:v>
-      </x:c>
-      <x:c r="C15" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) なしを型・必須・桁・業務Ruleで検証。3) notificationsを参照/更新。4) 参照の境界でCommit/Rollback。5) count Integerを共通Response形式で返却。</x:v>
-      </x:c>
-      <x:c r="D15" s="67" t="str">
-        <x:v>本人通知のみ</x:v>
-      </x:c>
-      <x:c r="E15" s="67" t="str">
-        <x:v>参照</x:v>
-      </x:c>
-      <x:c r="F15" s="67" t="str">
-        <x:v>COMMON-5000</x:v>
-      </x:c>
-      <x:c r="G15" s="67" t="str">
-        <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="30" customHeight="1">
-      <x:c r="A16" s="67" t="str">
-        <x:v>API-NTF-003</x:v>
-      </x:c>
-      <x:c r="B16" s="67" t="str">
-        <x:v>既読化</x:v>
-      </x:c>
-      <x:c r="C16" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) path: idを型・必須・桁・業務Ruleで検証。3) notificationsを参照/更新。4) TX-NTF-READの境界でCommit/Rollback。5) id,isRead,readAtを共通Response形式で返却。</x:v>
-      </x:c>
-      <x:c r="D16" s="67" t="str">
-        <x:v>受信者本人</x:v>
-      </x:c>
-      <x:c r="E16" s="67" t="str">
-        <x:v>TX-024</x:v>
-      </x:c>
-      <x:c r="F16" s="67" t="str">
-        <x:v>COMMON-4040/AUTH-4006</x:v>
-      </x:c>
-      <x:c r="G16" s="67" t="str">
-        <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="30" customHeight="1">
-      <x:c r="A17" s="67" t="str">
-        <x:v>API-NTF-004</x:v>
-      </x:c>
-      <x:c r="B17" s="67" t="str">
-        <x:v>全件既読</x:v>
-      </x:c>
-      <x:c r="C17" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) body: before DateTime?を型・必須・桁・業務Ruleで検証。3) notificationsを参照/更新。4) TX-NTF-READの境界でCommit/Rollback。5) updatedCountを共通Response形式で返却。</x:v>
-      </x:c>
-      <x:c r="D17" s="67" t="str">
-        <x:v>受信者本人</x:v>
+        <x:v>02／13_API権限対応 API-NTF-004
+Permission: -（認証/本人共通）
+Data Scope: DS-NTF-004</x:v>
       </x:c>
       <x:c r="E17" s="67" t="str">
         <x:v>TX-024</x:v>
@@ -3883,6 +3646,12 @@
       </x:c>
       <x:c r="G17" s="67" t="str">
         <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
+      </x:c>
+      <x:c r="H17" s="203" t="str">
+        <x:v>notifications</x:v>
+      </x:c>
+      <x:c r="I17" s="203" t="str">
+        <x:v>SCR-022</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3894,7 +3663,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -3949,8 +3718,8 @@
       <x:c r="C3" s="139"/>
       <x:c r="D3" s="139"/>
       <x:c r="E3" s="139"/>
-      <x:c r="F3" s="174" t="str">
-        <x:v>文書番号</x:v>
+      <x:c r="F3" s="246" t="str">
+        <x:v>章ID</x:v>
       </x:c>
       <x:c r="G3" s="139" t="str">
         <x:v>CW-BD-14-FIELD</x:v>
@@ -3964,8 +3733,8 @@
       <x:c r="A4" s="174" t="str">
         <x:v>版数</x:v>
       </x:c>
-      <x:c r="B4" s="139" t="str">
-        <x:v>Ver.1.8</x:v>
+      <x:c r="B4" s="63" t="str">
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="C4" s="139"/>
       <x:c r="D4" s="139"/>
@@ -3973,8 +3742,8 @@
       <x:c r="F4" s="174" t="str">
         <x:v>改訂日</x:v>
       </x:c>
-      <x:c r="G4" s="139" t="str">
-        <x:v>2026-08-12</x:v>
+      <x:c r="G4" s="63" t="str">
+        <x:v>2026-09-24</x:v>
       </x:c>
       <x:c r="H4" s="139"/>
       <x:c r="I4" s="139"/>
@@ -4242,39 +4011,17 @@
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
-      <x:c r="A14" s="67" t="str">
-        <x:v>API-RPT-001</x:v>
-      </x:c>
-      <x:c r="B14" s="67" t="str">
-        <x:v>Request</x:v>
-      </x:c>
-      <x:c r="C14" s="67" t="str">
-        <x:v>query</x:v>
-      </x:c>
-      <x:c r="D14" s="67" t="str">
-        <x:v>request.query.missing</x:v>
-      </x:c>
-      <x:c r="E14" s="67" t="str">
-        <x:v>Boolean</x:v>
-      </x:c>
-      <x:c r="F14" s="67" t="str">
-        <x:v>任意</x:v>
-      </x:c>
-      <x:c r="G14" s="67" t="str">
-        <x:v>-</x:v>
-      </x:c>
-      <x:c r="H14" s="67" t="str">
-        <x:v>-</x:v>
-      </x:c>
-      <x:c r="I14" s="67" t="str">
-        <x:v>可</x:v>
-      </x:c>
-      <x:c r="J14" s="67" t="str">
-        <x:v>未提出のみ</x:v>
-      </x:c>
-      <x:c r="K14" s="67" t="str">
-        <x:v>算出（daily_reports存在しない）</x:v>
-      </x:c>
+      <x:c r="A14" s="67"/>
+      <x:c r="B14" s="67"/>
+      <x:c r="C14" s="67"/>
+      <x:c r="D14" s="67"/>
+      <x:c r="E14" s="67"/>
+      <x:c r="F14" s="67"/>
+      <x:c r="G14" s="67"/>
+      <x:c r="H14" s="67"/>
+      <x:c r="I14" s="67"/>
+      <x:c r="J14" s="67"/>
+      <x:c r="K14" s="67"/>
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
       <x:c r="A15" s="67" t="str">
@@ -4786,7 +4533,7 @@
         <x:v>任意</x:v>
       </x:c>
       <x:c r="G29" s="67" t="str">
-        <x:v>最大100</x:v>
+        <x:v>最大200</x:v>
       </x:c>
       <x:c r="H29" s="67" t="str">
         <x:v>-</x:v>
@@ -4821,10 +4568,10 @@
         <x:v>必須</x:v>
       </x:c>
       <x:c r="G30" s="67" t="str">
-        <x:v>0..24</x:v>
+        <x:v>0超～24以下、小数2桁</x:v>
       </x:c>
       <x:c r="H30" s="67" t="str">
-        <x:v>0.25h単位</x:v>
+        <x:v>decimal(5,2)。入力値を保持し刻み変換・丸めをしない</x:v>
       </x:c>
       <x:c r="I30" s="67" t="str">
         <x:v>不可</x:v>
@@ -5521,7 +5268,7 @@
         <x:v>任意</x:v>
       </x:c>
       <x:c r="G50" s="67" t="str">
-        <x:v>最大100</x:v>
+        <x:v>最大200</x:v>
       </x:c>
       <x:c r="H50" s="67" t="str">
         <x:v>-</x:v>
@@ -5556,10 +5303,10 @@
         <x:v>必須</x:v>
       </x:c>
       <x:c r="G51" s="67" t="str">
-        <x:v>0..24</x:v>
+        <x:v>0超～24以下、小数2桁</x:v>
       </x:c>
       <x:c r="H51" s="67" t="str">
-        <x:v>0.25h単位</x:v>
+        <x:v>decimal(5,2)。入力値を保持し刻み変換・丸めをしない</x:v>
       </x:c>
       <x:c r="I51" s="67" t="str">
         <x:v>不可</x:v>
@@ -5661,7 +5408,7 @@
         <x:v>必須</x:v>
       </x:c>
       <x:c r="G54" s="67" t="str">
-        <x:v>最大4000</x:v>
+        <x:v>最大3000</x:v>
       </x:c>
       <x:c r="H54" s="67" t="str">
         <x:v>-</x:v>
@@ -5696,7 +5443,7 @@
         <x:v>任意</x:v>
       </x:c>
       <x:c r="G55" s="67" t="str">
-        <x:v>最大4000</x:v>
+        <x:v>最大3000</x:v>
       </x:c>
       <x:c r="H55" s="67" t="str">
         <x:v>-</x:v>
@@ -5731,7 +5478,7 @@
         <x:v>任意</x:v>
       </x:c>
       <x:c r="G56" s="67" t="str">
-        <x:v>最大2000</x:v>
+        <x:v>最大3000</x:v>
       </x:c>
       <x:c r="H56" s="67" t="str">
         <x:v>-</x:v>
@@ -5906,7 +5653,7 @@
         <x:v>必須</x:v>
       </x:c>
       <x:c r="G61" s="67" t="str">
-        <x:v>最大100</x:v>
+        <x:v>最大200</x:v>
       </x:c>
       <x:c r="H61" s="67" t="str">
         <x:v>-</x:v>
@@ -6081,7 +5828,7 @@
         <x:v>必須</x:v>
       </x:c>
       <x:c r="G66" s="67" t="str">
-        <x:v>最大4000</x:v>
+        <x:v>最大3000</x:v>
       </x:c>
       <x:c r="H66" s="67" t="str">
         <x:v>-</x:v>
@@ -6113,16 +5860,16 @@
         <x:v>String</x:v>
       </x:c>
       <x:c r="F67" s="67" t="str">
-        <x:v>任意</x:v>
+        <x:v>必須</x:v>
       </x:c>
       <x:c r="G67" s="67" t="str">
-        <x:v>最大4000</x:v>
+        <x:v>最大3000</x:v>
       </x:c>
       <x:c r="H67" s="67" t="str">
         <x:v>-</x:v>
       </x:c>
       <x:c r="I67" s="67" t="str">
-        <x:v>可</x:v>
+        <x:v>不可</x:v>
       </x:c>
       <x:c r="J67" s="67" t="str">
         <x:v>予定内容</x:v>
@@ -6151,7 +5898,7 @@
         <x:v>任意</x:v>
       </x:c>
       <x:c r="G68" s="67" t="str">
-        <x:v>最大2000</x:v>
+        <x:v>最大3000</x:v>
       </x:c>
       <x:c r="H68" s="67" t="str">
         <x:v>-</x:v>
@@ -6186,10 +5933,10 @@
         <x:v>必須</x:v>
       </x:c>
       <x:c r="G69" s="67" t="str">
-        <x:v>0超24以下</x:v>
+        <x:v>0超～24以下、小数2桁</x:v>
       </x:c>
       <x:c r="H69" s="67" t="str">
-        <x:v>decimal(5,2)</x:v>
+        <x:v>decimal(5,2)。入力値を保持し刻み変換・丸めをしない</x:v>
       </x:c>
       <x:c r="I69" s="67" t="str">
         <x:v>不可</x:v>
@@ -6571,7 +6318,7 @@
         <x:v>必須</x:v>
       </x:c>
       <x:c r="G80" s="67" t="str">
-        <x:v>最大4000</x:v>
+        <x:v>最大3000</x:v>
       </x:c>
       <x:c r="H80" s="67" t="str">
         <x:v>-</x:v>
@@ -6603,16 +6350,16 @@
         <x:v>String</x:v>
       </x:c>
       <x:c r="F81" s="67" t="str">
-        <x:v>任意</x:v>
+        <x:v>必須</x:v>
       </x:c>
       <x:c r="G81" s="67" t="str">
-        <x:v>最大4000</x:v>
+        <x:v>最大3000</x:v>
       </x:c>
       <x:c r="H81" s="67" t="str">
         <x:v>-</x:v>
       </x:c>
       <x:c r="I81" s="67" t="str">
-        <x:v>可</x:v>
+        <x:v>不可</x:v>
       </x:c>
       <x:c r="J81" s="67" t="str">
         <x:v>予定内容</x:v>
@@ -6641,7 +6388,7 @@
         <x:v>任意</x:v>
       </x:c>
       <x:c r="G82" s="67" t="str">
-        <x:v>最大2000</x:v>
+        <x:v>最大3000</x:v>
       </x:c>
       <x:c r="H82" s="67" t="str">
         <x:v>-</x:v>
@@ -6676,10 +6423,10 @@
         <x:v>必須</x:v>
       </x:c>
       <x:c r="G83" s="67" t="str">
-        <x:v>0超24以下</x:v>
+        <x:v>0超～24以下、小数2桁</x:v>
       </x:c>
       <x:c r="H83" s="67" t="str">
-        <x:v>decimal(5,2)</x:v>
+        <x:v>decimal(5,2)。入力値を保持し刻み変換・丸めをしない</x:v>
       </x:c>
       <x:c r="I83" s="67" t="str">
         <x:v>不可</x:v>
@@ -7041,7 +6788,7 @@
         <x:v>daily_reports.id</x:v>
       </x:c>
     </x:row>
-    <x:row r="94" ht="15" hidden="0" customHeight="1">
+    <x:row r="94" ht="65" hidden="0" customHeight="1">
       <x:c r="A94" s="67" t="str">
         <x:v>API-RPT-005</x:v>
       </x:c>
@@ -7058,19 +6805,19 @@
         <x:v>Integer</x:v>
       </x:c>
       <x:c r="F94" s="67" t="str">
-        <x:v>任意</x:v>
+        <x:v>必須</x:v>
       </x:c>
       <x:c r="G94" s="67" t="str">
-        <x:v>-</x:v>
+        <x:v>0以上の整数</x:v>
       </x:c>
       <x:c r="H94" s="67" t="str">
         <x:v>int32</x:v>
       </x:c>
       <x:c r="I94" s="67" t="str">
-        <x:v>可</x:v>
+        <x:v>不可</x:v>
       </x:c>
       <x:c r="J94" s="67" t="str">
-        <x:v>楽観Lock Version</x:v>
+        <x:v>Version。欠落/Null/形式不正=COMMON-4000、既存対象の不一致=COMMON-4090、削除済/不存在=COMMON-4040。権限確認後に判定。</x:v>
       </x:c>
       <x:c r="K94" s="67" t="str">
         <x:v>daily_reports.version</x:v>
@@ -7090,10 +6837,10 @@
         <x:v>response.body</x:v>
       </x:c>
       <x:c r="E95" s="67" t="str">
-        <x:v>Null</x:v>
+        <x:v>Bodyなし</x:v>
       </x:c>
       <x:c r="F95" s="67" t="str">
-        <x:v>任意</x:v>
+        <x:v>送信禁止</x:v>
       </x:c>
       <x:c r="G95" s="67" t="str">
         <x:v>-</x:v>
@@ -7102,16 +6849,16 @@
         <x:v>No Content</x:v>
       </x:c>
       <x:c r="I95" s="67" t="str">
-        <x:v>可</x:v>
+        <x:v>該当なし</x:v>
       </x:c>
       <x:c r="J95" s="67" t="str">
-        <x:v>Response Bodyなし</x:v>
+        <x:v>HTTP 204。JSON null、Envelope、空Objectを送信しない。</x:v>
       </x:c>
       <x:c r="K95" s="67" t="str">
         <x:v>-</x:v>
       </x:c>
     </x:row>
-    <x:row r="96" ht="15" hidden="0" customHeight="1">
+    <x:row r="96" ht="36" hidden="0" customHeight="1">
       <x:c r="A96" s="67" t="str">
         <x:v>API-RPT-006</x:v>
       </x:c>
@@ -7140,11 +6887,12 @@
         <x:v>可</x:v>
       </x:c>
       <x:c r="J96" s="67" t="str">
-        <x:v>date</x:v>
+        <x:v>催報対象日。省略=当日JST、未来不可、単日。</x:v>
       </x:c>
       <x:c r="K96" s="67" t="str">
         <x:v>daily_reports.report_date</x:v>
       </x:c>
+      <x:c r="L96" s="241"/>
     </x:row>
     <x:row r="97" ht="15" hidden="0" customHeight="1">
       <x:c r="A97" s="67" t="str">
@@ -7461,7 +7209,7 @@
         <x:v>-</x:v>
       </x:c>
     </x:row>
-    <x:row r="106" ht="15" hidden="0" customHeight="1">
+    <x:row r="106" ht="40" hidden="0" customHeight="1">
       <x:c r="A106" s="67" t="str">
         <x:v>API-RPT-006</x:v>
       </x:c>
@@ -7472,7 +7220,7 @@
         <x:v>body</x:v>
       </x:c>
       <x:c r="D106" s="67" t="str">
-        <x:v>response.body.data.content[].id</x:v>
+        <x:v>response.body.data.content[].employeeId</x:v>
       </x:c>
       <x:c r="E106" s="67" t="str">
         <x:v>Long</x:v>
@@ -7495,6 +7243,7 @@
       <x:c r="K106" s="67" t="str">
         <x:v>employees.id</x:v>
       </x:c>
+      <x:c r="L106" s="241"/>
     </x:row>
     <x:row r="107" ht="15" hidden="0" customHeight="1">
       <x:c r="A107" s="67" t="str">
@@ -7531,7 +7280,7 @@
         <x:v>employees.employee_code</x:v>
       </x:c>
     </x:row>
-    <x:row r="108" ht="15" hidden="0" customHeight="1">
+    <x:row r="108" ht="40" hidden="0" customHeight="1">
       <x:c r="A108" s="67" t="str">
         <x:v>API-RPT-006</x:v>
       </x:c>
@@ -7542,7 +7291,7 @@
         <x:v>body</x:v>
       </x:c>
       <x:c r="D108" s="67" t="str">
-        <x:v>response.body.data.content[].name</x:v>
+        <x:v>response.body.data.content[].employeeName</x:v>
       </x:c>
       <x:c r="E108" s="67" t="str">
         <x:v>String</x:v>
@@ -7565,8 +7314,9 @@
       <x:c r="K108" s="67" t="str">
         <x:v>employees.name</x:v>
       </x:c>
-    </x:row>
-    <x:row r="109" ht="15" hidden="0" customHeight="1">
+      <x:c r="L108" s="241"/>
+    </x:row>
+    <x:row r="109" ht="40" hidden="0" customHeight="1">
       <x:c r="A109" s="67" t="str">
         <x:v>API-RPT-006</x:v>
       </x:c>
@@ -7577,31 +7327,32 @@
         <x:v>body</x:v>
       </x:c>
       <x:c r="D109" s="67" t="str">
-        <x:v>response.body.data.content[].nameKana</x:v>
+        <x:v>response.body.data.content[].projectId</x:v>
       </x:c>
       <x:c r="E109" s="67" t="str">
-        <x:v>String</x:v>
+        <x:v>Long</x:v>
       </x:c>
       <x:c r="F109" s="67" t="str">
-        <x:v>任意</x:v>
+        <x:v>必須</x:v>
       </x:c>
       <x:c r="G109" s="67" t="str">
-        <x:v>最大100</x:v>
+        <x:v>-</x:v>
       </x:c>
       <x:c r="H109" s="67" t="str">
-        <x:v>全角Kana</x:v>
+        <x:v>int64</x:v>
       </x:c>
       <x:c r="I109" s="67" t="str">
-        <x:v>可</x:v>
+        <x:v>不可</x:v>
       </x:c>
       <x:c r="J109" s="67" t="str">
-        <x:v>氏名Kana</x:v>
+        <x:v>PJ ID</x:v>
       </x:c>
       <x:c r="K109" s="67" t="str">
-        <x:v>employees.name_kana</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="110" ht="15" hidden="0" customHeight="1">
+        <x:v>projects.id</x:v>
+      </x:c>
+      <x:c r="L109" s="241"/>
+    </x:row>
+    <x:row r="110" ht="40" hidden="0" customHeight="1">
       <x:c r="A110" s="67" t="str">
         <x:v>API-RPT-006</x:v>
       </x:c>
@@ -7612,7 +7363,7 @@
         <x:v>body</x:v>
       </x:c>
       <x:c r="D110" s="67" t="str">
-        <x:v>response.body.data.content[].email</x:v>
+        <x:v>response.body.data.content[].projectCode</x:v>
       </x:c>
       <x:c r="E110" s="67" t="str">
         <x:v>String</x:v>
@@ -7621,22 +7372,23 @@
         <x:v>必須</x:v>
       </x:c>
       <x:c r="G110" s="67" t="str">
-        <x:v>最大255</x:v>
+        <x:v>最大30</x:v>
       </x:c>
       <x:c r="H110" s="67" t="str">
-        <x:v>email</x:v>
+        <x:v>-</x:v>
       </x:c>
       <x:c r="I110" s="67" t="str">
         <x:v>不可</x:v>
       </x:c>
       <x:c r="J110" s="67" t="str">
-        <x:v>Mail</x:v>
+        <x:v>PJ番号</x:v>
       </x:c>
       <x:c r="K110" s="67" t="str">
-        <x:v>employees.email</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="111" ht="15" hidden="0" customHeight="1">
+        <x:v>projects.project_code</x:v>
+      </x:c>
+      <x:c r="L110" s="241"/>
+    </x:row>
+    <x:row r="111" ht="36" hidden="0" customHeight="1">
       <x:c r="A111" s="67" t="str">
         <x:v>API-RPT-006</x:v>
       </x:c>
@@ -7665,13 +7417,14 @@
         <x:v>不可</x:v>
       </x:c>
       <x:c r="J111" s="67" t="str">
-        <x:v>部門ID</x:v>
+        <x:v>現在部門ID</x:v>
       </x:c>
       <x:c r="K111" s="67" t="str">
         <x:v>employees.department_id</x:v>
       </x:c>
-    </x:row>
-    <x:row r="112" ht="15" hidden="0" customHeight="1">
+      <x:c r="L111" s="241"/>
+    </x:row>
+    <x:row r="112" ht="36" hidden="0" customHeight="1">
       <x:c r="A112" s="67" t="str">
         <x:v>API-RPT-006</x:v>
       </x:c>
@@ -7700,13 +7453,14 @@
         <x:v>不可</x:v>
       </x:c>
       <x:c r="J112" s="67" t="str">
-        <x:v>部門名</x:v>
+        <x:v>現在部門名</x:v>
       </x:c>
       <x:c r="K112" s="67" t="str">
         <x:v>departments.department_name</x:v>
       </x:c>
-    </x:row>
-    <x:row r="113" ht="15" hidden="0" customHeight="1">
+      <x:c r="L112" s="241"/>
+    </x:row>
+    <x:row r="113" ht="40" hidden="0" customHeight="1">
       <x:c r="A113" s="67" t="str">
         <x:v>API-RPT-006</x:v>
       </x:c>
@@ -7717,31 +7471,32 @@
         <x:v>body</x:v>
       </x:c>
       <x:c r="D113" s="67" t="str">
-        <x:v>response.body.data.content[].position</x:v>
+        <x:v>response.body.data.content[].projectName</x:v>
       </x:c>
       <x:c r="E113" s="67" t="str">
         <x:v>String</x:v>
       </x:c>
       <x:c r="F113" s="67" t="str">
-        <x:v>任意</x:v>
+        <x:v>必須</x:v>
       </x:c>
       <x:c r="G113" s="67" t="str">
-        <x:v>最大100</x:v>
+        <x:v>最大200</x:v>
       </x:c>
       <x:c r="H113" s="67" t="str">
         <x:v>-</x:v>
       </x:c>
       <x:c r="I113" s="67" t="str">
-        <x:v>可</x:v>
+        <x:v>不可</x:v>
       </x:c>
       <x:c r="J113" s="67" t="str">
-        <x:v>職位</x:v>
+        <x:v>PJ名</x:v>
       </x:c>
       <x:c r="K113" s="67" t="str">
-        <x:v>employees.position</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="114" ht="15" hidden="0" customHeight="1">
+        <x:v>projects.project_name</x:v>
+      </x:c>
+      <x:c r="L113" s="241"/>
+    </x:row>
+    <x:row r="114" ht="40" hidden="0" customHeight="1">
       <x:c r="A114" s="67" t="str">
         <x:v>API-RPT-006</x:v>
       </x:c>
@@ -7752,31 +7507,32 @@
         <x:v>body</x:v>
       </x:c>
       <x:c r="D114" s="67" t="str">
-        <x:v>response.body.data.content[].employmentStatus</x:v>
+        <x:v>response.body.data.content[].reportDate</x:v>
       </x:c>
       <x:c r="E114" s="67" t="str">
-        <x:v>String</x:v>
+        <x:v>Date</x:v>
       </x:c>
       <x:c r="F114" s="67" t="str">
         <x:v>必須</x:v>
       </x:c>
       <x:c r="G114" s="67" t="str">
-        <x:v>最大20</x:v>
+        <x:v>-</x:v>
       </x:c>
       <x:c r="H114" s="67" t="str">
-        <x:v>EMPLOYED/LEFT</x:v>
+        <x:v>yyyy-MM-dd</x:v>
       </x:c>
       <x:c r="I114" s="67" t="str">
         <x:v>不可</x:v>
       </x:c>
       <x:c r="J114" s="67" t="str">
-        <x:v>在籍状態</x:v>
+        <x:v>未提出対象日</x:v>
       </x:c>
       <x:c r="K114" s="67" t="str">
-        <x:v>employees.employment_status</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="115" ht="15" hidden="0" customHeight="1">
+        <x:v>request.query.date</x:v>
+      </x:c>
+      <x:c r="L114" s="241"/>
+    </x:row>
+    <x:row r="115" ht="40" hidden="0" customHeight="1">
       <x:c r="A115" s="67" t="str">
         <x:v>API-RPT-006</x:v>
       </x:c>
@@ -7787,10 +7543,10 @@
         <x:v>body</x:v>
       </x:c>
       <x:c r="D115" s="67" t="str">
-        <x:v>response.body.data.content[].joinedDate</x:v>
+        <x:v>response.body.data.content[].missing</x:v>
       </x:c>
       <x:c r="E115" s="67" t="str">
-        <x:v>Date</x:v>
+        <x:v>Boolean</x:v>
       </x:c>
       <x:c r="F115" s="67" t="str">
         <x:v>必須</x:v>
@@ -7799,87 +7555,44 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="H115" s="67" t="str">
-        <x:v>yyyy-MM-dd</x:v>
+        <x:v>true固定</x:v>
       </x:c>
       <x:c r="I115" s="67" t="str">
         <x:v>不可</x:v>
       </x:c>
       <x:c r="J115" s="67" t="str">
-        <x:v>入社日</x:v>
+        <x:v>未提出</x:v>
       </x:c>
       <x:c r="K115" s="67" t="str">
-        <x:v>employees.joined_date</x:v>
-      </x:c>
+        <x:v>導出</x:v>
+      </x:c>
+      <x:c r="L115" s="241"/>
     </x:row>
     <x:row r="116" ht="15" hidden="0" customHeight="1">
-      <x:c r="A116" s="67" t="str">
-        <x:v>API-RPT-006</x:v>
-      </x:c>
-      <x:c r="B116" s="67" t="str">
-        <x:v>Response</x:v>
-      </x:c>
-      <x:c r="C116" s="67" t="str">
-        <x:v>body</x:v>
-      </x:c>
-      <x:c r="D116" s="67" t="str">
-        <x:v>response.body.data.content[].leftDate</x:v>
-      </x:c>
-      <x:c r="E116" s="67" t="str">
-        <x:v>Date</x:v>
-      </x:c>
-      <x:c r="F116" s="67" t="str">
-        <x:v>任意</x:v>
-      </x:c>
-      <x:c r="G116" s="67" t="str">
-        <x:v>-</x:v>
-      </x:c>
-      <x:c r="H116" s="67" t="str">
-        <x:v>yyyy-MM-dd</x:v>
-      </x:c>
-      <x:c r="I116" s="67" t="str">
-        <x:v>可</x:v>
-      </x:c>
-      <x:c r="J116" s="67" t="str">
-        <x:v>退職日</x:v>
-      </x:c>
-      <x:c r="K116" s="67" t="str">
-        <x:v>employees.left_date</x:v>
-      </x:c>
+      <x:c r="A116" s="67"/>
+      <x:c r="B116" s="67"/>
+      <x:c r="C116" s="67"/>
+      <x:c r="D116" s="67"/>
+      <x:c r="E116" s="67"/>
+      <x:c r="F116" s="67"/>
+      <x:c r="G116" s="67"/>
+      <x:c r="H116" s="67"/>
+      <x:c r="I116" s="67"/>
+      <x:c r="J116" s="67"/>
+      <x:c r="K116" s="67"/>
     </x:row>
     <x:row r="117" ht="15" hidden="0" customHeight="1">
-      <x:c r="A117" s="67" t="str">
-        <x:v>API-RPT-006</x:v>
-      </x:c>
-      <x:c r="B117" s="67" t="str">
-        <x:v>Response</x:v>
-      </x:c>
-      <x:c r="C117" s="67" t="str">
-        <x:v>body</x:v>
-      </x:c>
-      <x:c r="D117" s="67" t="str">
-        <x:v>response.body.data.content[].version</x:v>
-      </x:c>
-      <x:c r="E117" s="67" t="str">
-        <x:v>Integer</x:v>
-      </x:c>
-      <x:c r="F117" s="67" t="str">
-        <x:v>必須</x:v>
-      </x:c>
-      <x:c r="G117" s="67" t="str">
-        <x:v>-</x:v>
-      </x:c>
-      <x:c r="H117" s="67" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="I117" s="67" t="str">
-        <x:v>不可</x:v>
-      </x:c>
-      <x:c r="J117" s="67" t="str">
-        <x:v>Version</x:v>
-      </x:c>
-      <x:c r="K117" s="67" t="str">
-        <x:v>employees.version</x:v>
-      </x:c>
+      <x:c r="A117" s="67"/>
+      <x:c r="B117" s="67"/>
+      <x:c r="C117" s="67"/>
+      <x:c r="D117" s="67"/>
+      <x:c r="E117" s="67"/>
+      <x:c r="F117" s="67"/>
+      <x:c r="G117" s="67"/>
+      <x:c r="H117" s="67"/>
+      <x:c r="I117" s="67"/>
+      <x:c r="J117" s="67"/>
+      <x:c r="K117" s="67"/>
     </x:row>
     <x:row r="118" ht="15" hidden="0" customHeight="1">
       <x:c r="A118" s="67" t="str">
@@ -9737,39 +9450,17 @@
       </x:c>
     </x:row>
     <x:row r="171" ht="15" hidden="0" customHeight="1">
-      <x:c r="A171" s="67" t="str">
-        <x:v>API-TASK-009</x:v>
-      </x:c>
-      <x:c r="B171" s="67" t="str">
-        <x:v>Request</x:v>
-      </x:c>
-      <x:c r="C171" s="67" t="str">
-        <x:v>path</x:v>
-      </x:c>
-      <x:c r="D171" s="67" t="str">
-        <x:v>request.path.id</x:v>
-      </x:c>
-      <x:c r="E171" s="67" t="str">
-        <x:v>Long</x:v>
-      </x:c>
-      <x:c r="F171" s="67" t="str">
-        <x:v>必須</x:v>
-      </x:c>
-      <x:c r="G171" s="67" t="str">
-        <x:v>-</x:v>
-      </x:c>
-      <x:c r="H171" s="67" t="str">
-        <x:v>int64</x:v>
-      </x:c>
-      <x:c r="I171" s="67" t="str">
-        <x:v>不可</x:v>
-      </x:c>
-      <x:c r="J171" s="67" t="str">
-        <x:v>Task ID</x:v>
-      </x:c>
-      <x:c r="K171" s="67" t="str">
-        <x:v>tasks.id</x:v>
-      </x:c>
+      <x:c r="A171" s="67"/>
+      <x:c r="B171" s="67"/>
+      <x:c r="C171" s="67"/>
+      <x:c r="D171" s="67"/>
+      <x:c r="E171" s="67"/>
+      <x:c r="F171" s="67"/>
+      <x:c r="G171" s="67"/>
+      <x:c r="H171" s="67"/>
+      <x:c r="I171" s="67"/>
+      <x:c r="J171" s="67"/>
+      <x:c r="K171" s="67"/>
     </x:row>
     <x:row r="172" ht="15" hidden="0" customHeight="1">
       <x:c r="A172" s="67" t="str">
@@ -9820,9 +9511,7 @@
       <x:c r="K173" s="203"/>
     </x:row>
     <x:row r="174">
-      <x:c r="A174" s="186" t="str">
-        <x:v>JSON Path、型、必須、桁、Enum、Null、DB／生成元を外部契約として固定する。Path IDはDB型BIGINTに合わせLongとする。</x:v>
-      </x:c>
+      <x:c r="A174" s="186" t="str"/>
       <x:c r="B174" s="186"/>
       <x:c r="C174" s="186"/>
       <x:c r="D174" s="186"/>
@@ -9847,6 +9536,78 @@
       <x:c r="J175" s="186"/>
       <x:c r="K175" s="186"/>
     </x:row>
+    <x:row r="176" ht="40" customHeight="1">
+      <x:c r="A176" s="241" t="str">
+        <x:v>API-RPT-006</x:v>
+      </x:c>
+      <x:c r="B176" s="241" t="str">
+        <x:v>Request</x:v>
+      </x:c>
+      <x:c r="C176" s="241" t="str">
+        <x:v>query</x:v>
+      </x:c>
+      <x:c r="D176" s="241" t="str">
+        <x:v>request.query.employeeId</x:v>
+      </x:c>
+      <x:c r="E176" s="241" t="str">
+        <x:v>Long</x:v>
+      </x:c>
+      <x:c r="F176" s="241" t="str">
+        <x:v>任意</x:v>
+      </x:c>
+      <x:c r="G176" s="241" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="H176" s="241" t="str">
+        <x:v>int64</x:v>
+      </x:c>
+      <x:c r="I176" s="241" t="str">
+        <x:v>可</x:v>
+      </x:c>
+      <x:c r="J176" s="241" t="str">
+        <x:v>未指定は全件（権限範囲内）。現在の社員/部門で絞込。</x:v>
+      </x:c>
+      <x:c r="K176" s="241" t="str">
+        <x:v>employees.id</x:v>
+      </x:c>
+      <x:c r="L176" s="241"/>
+    </x:row>
+    <x:row r="177" ht="40" customHeight="1">
+      <x:c r="A177" s="241" t="str">
+        <x:v>API-RPT-006</x:v>
+      </x:c>
+      <x:c r="B177" s="241" t="str">
+        <x:v>Request</x:v>
+      </x:c>
+      <x:c r="C177" s="241" t="str">
+        <x:v>query</x:v>
+      </x:c>
+      <x:c r="D177" s="241" t="str">
+        <x:v>request.query.departmentId</x:v>
+      </x:c>
+      <x:c r="E177" s="241" t="str">
+        <x:v>Long</x:v>
+      </x:c>
+      <x:c r="F177" s="241" t="str">
+        <x:v>任意</x:v>
+      </x:c>
+      <x:c r="G177" s="241" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="H177" s="241" t="str">
+        <x:v>int64</x:v>
+      </x:c>
+      <x:c r="I177" s="241" t="str">
+        <x:v>可</x:v>
+      </x:c>
+      <x:c r="J177" s="241" t="str">
+        <x:v>未指定は全件（権限範囲内）。現在の社員/部門で絞込。</x:v>
+      </x:c>
+      <x:c r="K177" s="241" t="str">
+        <x:v>employees.department_id</x:v>
+      </x:c>
+      <x:c r="L177" s="241"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:K2"/>
@@ -9858,14 +9619,14 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="72" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="82" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="100" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="100" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="28" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="38" hidden="0" customWidth="1"/>
@@ -9899,8 +9660,8 @@
         <x:v>Company WorkHub</x:v>
       </x:c>
       <x:c r="C3" s="139"/>
-      <x:c r="D3" s="174" t="str">
-        <x:v>文書番号</x:v>
+      <x:c r="D3" s="246" t="str">
+        <x:v>章ID</x:v>
       </x:c>
       <x:c r="E3" s="139" t="str">
         <x:v>CW-BD-14-SAMPLE</x:v>
@@ -9912,18 +9673,29 @@
       <x:c r="A4" s="174" t="str">
         <x:v>版数</x:v>
       </x:c>
-      <x:c r="B4" s="139" t="str">
-        <x:v>Ver.1.8</x:v>
+      <x:c r="B4" s="63" t="str">
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="C4" s="139"/>
       <x:c r="D4" s="174" t="str">
         <x:v>改訂日</x:v>
       </x:c>
-      <x:c r="E4" s="139" t="str">
-        <x:v>2026-08-12</x:v>
+      <x:c r="E4" s="63" t="str">
+        <x:v>2026-09-24</x:v>
       </x:c>
       <x:c r="F4" s="139"/>
       <x:c r="G4" s="139"/>
+    </x:row>
+    <x:row r="5" ht="42" customHeight="1">
+      <x:c r="A5" s="203" t="str">
+        <x:v>参考資料。Contract正本は23_API項目定義。Request例は送信区分別の表示用Object（そのまま送るJSONではない）。認証等の共通Headerは10／19参照。Binary PartはFile名で表記。各行は独立した例。</x:v>
+      </x:c>
+      <x:c r="B5" s="203"/>
+      <x:c r="C5" s="203"/>
+      <x:c r="D5" s="203"/>
+      <x:c r="E5" s="203"/>
+      <x:c r="F5" s="203"/>
+      <x:c r="G5" s="203"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="175" t="str">
@@ -9959,7 +9731,7 @@
         <x:v>備考</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="120" customHeight="1">
+    <x:row r="8" ht="100" customHeight="1">
       <x:c r="A8" s="67" t="str">
         <x:v>API-RPT-001</x:v>
       </x:c>
@@ -9967,49 +9739,10 @@
         <x:v>日報検索</x:v>
       </x:c>
       <x:c r="C8" s="67" t="str">
-        <x:v>{
-  "query": {
-    "employeeId": 1001,
-    "departmentId": 1001,
-    "projectId": 1001,
-    "dateFrom": "2026-08-10",
-    "dateTo": "2026-08-10",
-    "hasIssue": true,
-    "missing": true,
-    "page": 0,
-    "size": 20,
-    "sort": "sample"
-  }
-}</x:v>
+        <x:v>{"query": {"employeeId": 1001, "departmentId": 1001, "projectId": 1001, "dateFrom": "2026-08-10", "dateTo": "2026-08-10", "hasIssue": true, "page": 0, "size": 20}}</x:v>
       </x:c>
       <x:c r="D8" s="67" t="str">
-        <x:v>{
-  "code": "COMMON-0000",
-  "message": "処理成功",
-  "timestamp": "2026-08-10T10:00:00+09:00",
-  "traceId": "7f3a9c01e2b44d8a",
-  "data": {
-    "content": [
-      {
-        "id": 1001,
-        "reportDate": "2026-08-10",
-        "employeeId": 1001,
-        "employeeName": "サンプル",
-        "projectId": 1001,
-        "projectName": "サンプル",
-        "workingHours": 7.5,
-        "hasIssue": true,
-        "version": 1
-      }
-    ],
-    "page": 1,
-    "size": 1,
-    "totalElements": 1001,
-    "totalPages": 1,
-    "first": true,
-    "last": true
-  }
-}</x:v>
+        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-10T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"content": [{"id": 1001, "reportDate": "2026-08-10", "employeeId": 1001, "employeeName": "サンプル", "projectId": 1001, "projectName": "サンプル", "workingHours": 7.5, "hasIssue": true, "version": 1}], "page": 0, "size": 20, "totalElements": 1, "totalPages": 1, "first": true, "last": true}}</x:v>
       </x:c>
       <x:c r="E8" s="67" t="str">
         <x:v>200</x:v>
@@ -10021,7 +9754,7 @@
         <x:v>値は例。項目定義を正とする</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="120" customHeight="1">
+    <x:row r="9" ht="115" customHeight="1">
       <x:c r="A9" s="67" t="str">
         <x:v>API-RPT-002</x:v>
       </x:c>
@@ -10029,43 +9762,10 @@
         <x:v>日報詳細</x:v>
       </x:c>
       <x:c r="C9" s="67" t="str">
-        <x:v>{
-  "path": {
-    "id": 1001
-  }
-}</x:v>
+        <x:v>{"path": {"id": 1001}}</x:v>
       </x:c>
       <x:c r="D9" s="67" t="str">
-        <x:v>{
-  "code": "COMMON-0000",
-  "message": "処理成功",
-  "timestamp": "2026-08-10T10:00:00+09:00",
-  "traceId": "7f3a9c01e2b44d8a",
-  "data": {
-    "id": 1001,
-    "reportDate": "2026-08-10",
-    "employeeId": 1001,
-    "employeeName": "サンプル",
-    "projectId": 1001,
-    "projectName": "サンプル",
-    "workingHours": 7.5,
-    "hasIssue": true,
-    "version": 1,
-    "completedWork": "sample",
-    "plannedWork": "sample",
-    "issues": "sample",
-    "tasks": [
-      {
-        "id": 1001,
-        "taskCode": "sample",
-        "projectId": 1001,
-        "projectName": "サンプル",
-        "title": "sample",
-        "assigneeId": 1001
-      }
-    ]
-  }
-}</x:v>
+        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-10T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"id": 1001, "reportDate": "2026-08-10", "employeeId": 1001, "employeeName": "サンプル", "projectId": 1001, "projectName": "サンプル", "workingHours": 7.5, "hasIssue": true, "version": 1, "completedWork": "sample", "plannedWork": "sample", "issues": "sample", "tasks": [{"id": 1001, "taskCode": "sample", "projectId": 1001, "projectName": "サンプル", "title": "sample", "assigneeId": 1001}]}}</x:v>
       </x:c>
       <x:c r="E9" s="67" t="str">
         <x:v>200</x:v>
@@ -10077,7 +9777,7 @@
         <x:v>値は例。項目定義を正とする</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="120" customHeight="1">
+    <x:row r="10" ht="100" customHeight="1">
       <x:c r="A10" s="67" t="str">
         <x:v>API-RPT-003</x:v>
       </x:c>
@@ -10085,35 +9785,10 @@
         <x:v>日報登録</x:v>
       </x:c>
       <x:c r="C10" s="67" t="str">
-        <x:v>{
-  "body": {
-    "reportDate": "2026-08-10",
-    "projectId": 1001,
-    "completedWork": "sample",
-    "plannedWork": "sample",
-    "issues": "sample",
-    "workingHours": 7.5,
-    "taskIds": [
-      1001,
-      1002
-    ]
-  },
-  "header": {
-    "X-Idempotency-Key": "550e8400-e29b-41d4-a716-446655440000"
-  }
-}</x:v>
+        <x:v>{"body": {"reportDate": "2026-08-10", "projectId": 1001, "completedWork": "sample", "plannedWork": "sample", "issues": "sample", "workingHours": 7.5, "taskIds": [1001, 1002]}, "header": {"X-Idempotency-Key": "550e8400-e29b-41d4-a716-446655440000"}}</x:v>
       </x:c>
       <x:c r="D10" s="67" t="str">
-        <x:v>{
-  "code": "COMMON-0000",
-  "message": "処理成功",
-  "timestamp": "2026-08-10T10:00:00+09:00",
-  "traceId": "7f3a9c01e2b44d8a",
-  "data": {
-    "id": 1001,
-    "version": 1
-  }
-}</x:v>
+        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-10T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"id": 1001, "version": 1}}</x:v>
       </x:c>
       <x:c r="E10" s="67" t="str">
         <x:v>201</x:v>
@@ -10125,7 +9800,7 @@
         <x:v>値は例。項目定義を正とする</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="120" customHeight="1">
+    <x:row r="11" ht="100" customHeight="1">
       <x:c r="A11" s="67" t="str">
         <x:v>API-RPT-004</x:v>
       </x:c>
@@ -10133,34 +9808,10 @@
         <x:v>日報更新</x:v>
       </x:c>
       <x:c r="C11" s="67" t="str">
-        <x:v>{
-  "path": {
-    "id": 1001
-  },
-  "body": {
-    "completedWork": "sample",
-    "plannedWork": "sample",
-    "issues": "sample",
-    "workingHours": 7.5,
-    "taskIds": [
-      1001,
-      1002
-    ],
-    "version": 1
-  }
-}</x:v>
+        <x:v>{"path": {"id": 1001}, "body": {"completedWork": "sample", "plannedWork": "sample", "issues": "sample", "workingHours": 7.5, "taskIds": [1001, 1002], "version": 1}}</x:v>
       </x:c>
       <x:c r="D11" s="67" t="str">
-        <x:v>{
-  "code": "COMMON-0000",
-  "message": "処理成功",
-  "timestamp": "2026-08-10T10:00:00+09:00",
-  "traceId": "7f3a9c01e2b44d8a",
-  "data": {
-    "id": 1001,
-    "version": 1
-  }
-}</x:v>
+        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-10T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"id": 1001, "version": 2}}</x:v>
       </x:c>
       <x:c r="E11" s="67" t="str">
         <x:v>200</x:v>
@@ -10172,7 +9823,7 @@
         <x:v>値は例。項目定義を正とする</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="120" customHeight="1">
+    <x:row r="12" ht="100" customHeight="1">
       <x:c r="A12" s="67" t="str">
         <x:v>API-RPT-005</x:v>
       </x:c>
@@ -10180,14 +9831,7 @@
         <x:v>日報削除</x:v>
       </x:c>
       <x:c r="C12" s="67" t="str">
-        <x:v>{
-  "path": {
-    "id": 1001
-  },
-  "query": {
-    "version": 1
-  }
-}</x:v>
+        <x:v>{"path": {"id": 1001}, "query": {"version": 1}}</x:v>
       </x:c>
       <x:c r="D12" s="67" t="str">
         <x:v>-（Response Bodyなし）</x:v>
@@ -10202,7 +9846,7 @@
         <x:v>値は例。項目定義を正とする</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="120" customHeight="1">
+    <x:row r="13" ht="115" customHeight="1">
       <x:c r="A13" s="67" t="str">
         <x:v>API-RPT-006</x:v>
       </x:c>
@@ -10210,46 +9854,10 @@
         <x:v>未提出者検索</x:v>
       </x:c>
       <x:c r="C13" s="67" t="str">
-        <x:v>{
-  "query": {
-    "date": "2026-08-10",
-    "projectId": 1001,
-    "page": 0,
-    "size": 20
-  }
-}</x:v>
+        <x:v>{"query": {"date": "2026-08-10", "projectId": 2001, "page": 0, "size": 20}}</x:v>
       </x:c>
       <x:c r="D13" s="67" t="str">
-        <x:v>{
-  "code": "COMMON-0000",
-  "message": "処理成功",
-  "timestamp": "2026-08-10T10:00:00+09:00",
-  "traceId": "7f3a9c01e2b44d8a",
-  "data": {
-    "content": [
-      {
-        "id": 1001,
-        "employeeCode": "sample",
-        "name": "サンプル",
-        "nameKana": "サンプル",
-        "email": "user@example.co.jp",
-        "departmentId": 1001,
-        "departmentName": "サンプル",
-        "position": "sample",
-        "employmentStatus": "EMPLOYED",
-        "joinedDate": "2026-08-10",
-        "leftDate": "2026-08-10",
-        "version": 1
-      }
-    ],
-    "page": 1,
-    "size": 1,
-    "totalElements": 1001,
-    "totalPages": 1,
-    "first": true,
-    "last": true
-  }
-}</x:v>
+        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-10T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"content": [{"employeeId": 1001, "employeeCode": "E001", "employeeName": "山田 太郎", "projectId": 2001, "projectCode": "PJ001", "departmentId": 1, "departmentName": "開発部", "projectName": "社内改善", "reportDate": "2026-08-10", "missing": true}], "page": 0, "size": 20, "totalElements": 1, "totalPages": 1, "first": true, "last": true}}</x:v>
       </x:c>
       <x:c r="E13" s="67" t="str">
         <x:v>200</x:v>
@@ -10261,7 +9869,7 @@
         <x:v>値は例。項目定義を正とする</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="120" customHeight="1">
+    <x:row r="14" ht="115" customHeight="1">
       <x:c r="A14" s="67" t="str">
         <x:v>API-NTF-001</x:v>
       </x:c>
@@ -10269,44 +9877,10 @@
         <x:v>通知一覧</x:v>
       </x:c>
       <x:c r="C14" s="67" t="str">
-        <x:v>{
-  "query": {
-    "read": true,
-    "type": "sample",
-    "page": 0,
-    "size": 20,
-    "sort": "sample"
-  }
-}</x:v>
+        <x:v>{"query": {"read": true, "type": "TASK_DUE", "page": 0, "size": 20}}</x:v>
       </x:c>
       <x:c r="D14" s="67" t="str">
-        <x:v>{
-  "code": "COMMON-0000",
-  "message": "処理成功",
-  "timestamp": "2026-08-10T10:00:00+09:00",
-  "traceId": "7f3a9c01e2b44d8a",
-  "data": {
-    "content": [
-      {
-        "id": 1001,
-        "notificationType": "TASK_DUE",
-        "title": "sample",
-        "content": "sample",
-        "relatedType": "TASK",
-        "relatedId": 1001,
-        "isRead": true,
-        "readAt": "2026-08-10T10:00:00+09:00",
-        "createdAt": "2026-08-10T10:00:00+09:00"
-      }
-    ],
-    "page": 1,
-    "size": 1,
-    "totalElements": 1001,
-    "totalPages": 1,
-    "first": true,
-    "last": true
-  }
-}</x:v>
+        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-10T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"content": [{"id": 1001, "notificationType": "TASK_DUE", "title": "sample", "content": "sample", "relatedType": "TASK", "relatedId": 1001, "isRead": true, "readAt": "2026-08-10T10:00:00+09:00", "createdAt": "2026-08-10T10:00:00+09:00"}], "page": 0, "size": 20, "totalElements": 1, "totalPages": 1, "first": true, "last": true}}</x:v>
       </x:c>
       <x:c r="E14" s="67" t="str">
         <x:v>200</x:v>
@@ -10318,7 +9892,7 @@
         <x:v>値は例。項目定義を正とする</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="120" customHeight="1">
+    <x:row r="15" ht="100" customHeight="1">
       <x:c r="A15" s="67" t="str">
         <x:v>API-NTF-002</x:v>
       </x:c>
@@ -10329,15 +9903,7 @@
         <x:v>{}</x:v>
       </x:c>
       <x:c r="D15" s="67" t="str">
-        <x:v>{
-  "code": "COMMON-0000",
-  "message": "処理成功",
-  "timestamp": "2026-08-10T10:00:00+09:00",
-  "traceId": "7f3a9c01e2b44d8a",
-  "data": {
-    "count": 1
-  }
-}</x:v>
+        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-10T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"count": 1}}</x:v>
       </x:c>
       <x:c r="E15" s="67" t="str">
         <x:v>200</x:v>
@@ -10349,7 +9915,7 @@
         <x:v>値は例。項目定義を正とする</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="120" customHeight="1">
+    <x:row r="16" ht="100" customHeight="1">
       <x:c r="A16" s="67" t="str">
         <x:v>API-NTF-003</x:v>
       </x:c>
@@ -10357,24 +9923,10 @@
         <x:v>既読化</x:v>
       </x:c>
       <x:c r="C16" s="67" t="str">
-        <x:v>{
-  "path": {
-    "id": 1001
-  }
-}</x:v>
+        <x:v>{"path": {"id": 1001}}</x:v>
       </x:c>
       <x:c r="D16" s="67" t="str">
-        <x:v>{
-  "code": "COMMON-0000",
-  "message": "処理成功",
-  "timestamp": "2026-08-10T10:00:00+09:00",
-  "traceId": "7f3a9c01e2b44d8a",
-  "data": {
-    "id": 1001,
-    "isRead": true,
-    "readAt": "2026-08-10T10:00:00+09:00"
-  }
-}</x:v>
+        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-10T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"id": 1001, "isRead": true, "readAt": "2026-08-10T10:00:00+09:00"}}</x:v>
       </x:c>
       <x:c r="E16" s="67" t="str">
         <x:v>200</x:v>
@@ -10386,7 +9938,7 @@
         <x:v>値は例。項目定義を正とする</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="120" customHeight="1">
+    <x:row r="17" ht="100" customHeight="1">
       <x:c r="A17" s="67" t="str">
         <x:v>API-NTF-004</x:v>
       </x:c>
@@ -10394,22 +9946,10 @@
         <x:v>全件既読</x:v>
       </x:c>
       <x:c r="C17" s="67" t="str">
-        <x:v>{
-  "body": {
-    "before": "2026-08-10T10:00:00+09:00"
-  }
-}</x:v>
+        <x:v>{"body": {"before": "2026-08-10T10:00:00+09:00"}}</x:v>
       </x:c>
       <x:c r="D17" s="67" t="str">
-        <x:v>{
-  "code": "COMMON-0000",
-  "message": "処理成功",
-  "timestamp": "2026-08-10T10:00:00+09:00",
-  "traceId": "7f3a9c01e2b44d8a",
-  "data": {
-    "updatedCount": 5
-  }
-}</x:v>
+        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-10T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"updatedCount": 5}}</x:v>
       </x:c>
       <x:c r="E17" s="67" t="str">
         <x:v>200</x:v>
@@ -10449,324 +9989,4 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="48" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="42" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="62" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="138" t="str">
-        <x:v>API権限対応</x:v>
-      </x:c>
-      <x:c r="B1" s="138"/>
-      <x:c r="C1" s="138"/>
-      <x:c r="D1" s="138"/>
-      <x:c r="E1" s="138"/>
-      <x:c r="F1" s="138"/>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="138"/>
-      <x:c r="B2" s="138"/>
-      <x:c r="C2" s="138"/>
-      <x:c r="D2" s="138"/>
-      <x:c r="E2" s="138"/>
-      <x:c r="F2" s="138"/>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="141" t="str">
-        <x:v>システム名</x:v>
-      </x:c>
-      <x:c r="B3" s="139" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="C3" s="141" t="str">
-        <x:v>文書番号</x:v>
-      </x:c>
-      <x:c r="D3" s="139" t="str">
-        <x:v>CW-BD-14-PERM</x:v>
-      </x:c>
-      <x:c r="E3" s="139"/>
-      <x:c r="F3" s="139"/>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="141" t="str">
-        <x:v>版数</x:v>
-      </x:c>
-      <x:c r="B4" s="139" t="str">
-        <x:v>Ver.1.8</x:v>
-      </x:c>
-      <x:c r="C4" s="141" t="str">
-        <x:v>改訂日</x:v>
-      </x:c>
-      <x:c r="D4" s="139" t="str">
-        <x:v>2026-08-12</x:v>
-      </x:c>
-      <x:c r="E4" s="139"/>
-      <x:c r="F4" s="139"/>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="142" t="str">
-        <x:v>1. API・Permission・Data範囲</x:v>
-      </x:c>
-      <x:c r="B6" s="142"/>
-      <x:c r="C6" s="142"/>
-      <x:c r="D6" s="142"/>
-      <x:c r="E6" s="142"/>
-      <x:c r="F6" s="142"/>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="147" t="str">
-        <x:v>API ID</x:v>
-      </x:c>
-      <x:c r="B7" s="147" t="str">
-        <x:v>API名</x:v>
-      </x:c>
-      <x:c r="C7" s="147" t="str">
-        <x:v>Permission Code</x:v>
-      </x:c>
-      <x:c r="D7" s="147" t="str">
-        <x:v>許可Role</x:v>
-      </x:c>
-      <x:c r="E7" s="147" t="str">
-        <x:v>Data範囲</x:v>
-      </x:c>
-      <x:c r="F7" s="147" t="str">
-        <x:v>判定方式</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="151" t="str">
-        <x:v>API-RPT-001</x:v>
-      </x:c>
-      <x:c r="B8" s="151" t="str">
-        <x:v>日報検索</x:v>
-      </x:c>
-      <x:c r="C8" s="151" t="str">
-        <x:v>PERM-RPT-SELF / PERM-RPT-TEAM</x:v>
-      </x:c>
-      <x:c r="D8" s="151" t="str">
-        <x:v>権限別</x:v>
-      </x:c>
-      <x:c r="E8" s="151" t="str">
-        <x:v>ADMIN=全社, PM=担当PJ, EMP=本人</x:v>
-      </x:c>
-      <x:c r="F8" s="151" t="str">
-        <x:v>hasAuthority('PERM-RPT-SELF') + Data範囲をServiceで再判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="151" t="str">
-        <x:v>API-RPT-002</x:v>
-      </x:c>
-      <x:c r="B9" s="151" t="str">
-        <x:v>日報詳細</x:v>
-      </x:c>
-      <x:c r="C9" s="151" t="str">
-        <x:v>PERM-RPT-SELF / PERM-RPT-TEAM</x:v>
-      </x:c>
-      <x:c r="D9" s="151" t="str">
-        <x:v>権限別</x:v>
-      </x:c>
-      <x:c r="E9" s="151" t="str">
-        <x:v>ADMIN=全社, PM=担当PJ, EMP=本人</x:v>
-      </x:c>
-      <x:c r="F9" s="151" t="str">
-        <x:v>hasAuthority('PERM-RPT-SELF') + Data範囲をServiceで再判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="151" t="str">
-        <x:v>API-RPT-003</x:v>
-      </x:c>
-      <x:c r="B10" s="151" t="str">
-        <x:v>日報登録</x:v>
-      </x:c>
-      <x:c r="C10" s="151" t="str">
-        <x:v>PERM-RPT-SELF</x:v>
-      </x:c>
-      <x:c r="D10" s="151" t="str">
-        <x:v>全員</x:v>
-      </x:c>
-      <x:c r="E10" s="151" t="str">
-        <x:v>本人; 当該PJ Member</x:v>
-      </x:c>
-      <x:c r="F10" s="151" t="str">
-        <x:v>hasAuthority('PERM-RPT-SELF') + Data範囲をServiceで再判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="151" t="str">
-        <x:v>API-RPT-004</x:v>
-      </x:c>
-      <x:c r="B11" s="151" t="str">
-        <x:v>日報更新</x:v>
-      </x:c>
-      <x:c r="C11" s="151" t="str">
-        <x:v>PERM-RPT-SELF</x:v>
-      </x:c>
-      <x:c r="D11" s="151" t="str">
-        <x:v>本人/管理者</x:v>
-      </x:c>
-      <x:c r="E11" s="151" t="str">
-        <x:v>本人=当日・前営業日, ADMIN=全期間</x:v>
-      </x:c>
-      <x:c r="F11" s="151" t="str">
-        <x:v>hasAuthority('PERM-RPT-SELF') + Data範囲をServiceで再判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="151" t="str">
-        <x:v>API-RPT-005</x:v>
-      </x:c>
-      <x:c r="B12" s="151" t="str">
-        <x:v>日報削除</x:v>
-      </x:c>
-      <x:c r="C12" s="151" t="str">
-        <x:v>PERM-RPT-SELF</x:v>
-      </x:c>
-      <x:c r="D12" s="151" t="str">
-        <x:v>本人/管理者</x:v>
-      </x:c>
-      <x:c r="E12" s="151" t="str">
-        <x:v>本人=当日・前営業日, ADMIN=全期間</x:v>
-      </x:c>
-      <x:c r="F12" s="151" t="str">
-        <x:v>hasAuthority('PERM-RPT-SELF') + Data範囲をServiceで再判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="151" t="str">
-        <x:v>API-RPT-006</x:v>
-      </x:c>
-      <x:c r="B13" s="151" t="str">
-        <x:v>未提出者検索</x:v>
-      </x:c>
-      <x:c r="C13" s="151" t="str">
-        <x:v>PERM-RPT-TEAM</x:v>
-      </x:c>
-      <x:c r="D13" s="151" t="str">
-        <x:v>管理者/担当PM</x:v>
-      </x:c>
-      <x:c r="E13" s="151" t="str">
-        <x:v>ADMIN=全社, PM=担当PJ</x:v>
-      </x:c>
-      <x:c r="F13" s="151" t="str">
-        <x:v>hasAuthority('PERM-RPT-TEAM') + Data範囲をServiceで再判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="151" t="str">
-        <x:v>API-NTF-001</x:v>
-      </x:c>
-      <x:c r="B14" s="151" t="str">
-        <x:v>通知一覧</x:v>
-      </x:c>
-      <x:c r="C14" s="151" t="str">
-        <x:v>-（認証/本人共通）</x:v>
-      </x:c>
-      <x:c r="D14" s="151" t="str">
-        <x:v>全員</x:v>
-      </x:c>
-      <x:c r="E14" s="151" t="str">
-        <x:v>本人通知のみ</x:v>
-      </x:c>
-      <x:c r="F14" s="151" t="str">
-        <x:v>認証・本人/共通条件をServiceで判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="151" t="str">
-        <x:v>API-NTF-002</x:v>
-      </x:c>
-      <x:c r="B15" s="151" t="str">
-        <x:v>未読件数</x:v>
-      </x:c>
-      <x:c r="C15" s="151" t="str">
-        <x:v>-（認証/本人共通）</x:v>
-      </x:c>
-      <x:c r="D15" s="151" t="str">
-        <x:v>全員</x:v>
-      </x:c>
-      <x:c r="E15" s="151" t="str">
-        <x:v>本人通知のみ</x:v>
-      </x:c>
-      <x:c r="F15" s="151" t="str">
-        <x:v>認証・本人/共通条件をServiceで判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="151" t="str">
-        <x:v>API-NTF-003</x:v>
-      </x:c>
-      <x:c r="B16" s="151" t="str">
-        <x:v>既読化</x:v>
-      </x:c>
-      <x:c r="C16" s="151" t="str">
-        <x:v>-（認証/本人共通）</x:v>
-      </x:c>
-      <x:c r="D16" s="151" t="str">
-        <x:v>本人</x:v>
-      </x:c>
-      <x:c r="E16" s="151" t="str">
-        <x:v>受信者本人</x:v>
-      </x:c>
-      <x:c r="F16" s="151" t="str">
-        <x:v>認証・本人/共通条件をServiceで判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="151" t="str">
-        <x:v>API-NTF-004</x:v>
-      </x:c>
-      <x:c r="B17" s="151" t="str">
-        <x:v>全件既読</x:v>
-      </x:c>
-      <x:c r="C17" s="151" t="str">
-        <x:v>-（認証/本人共通）</x:v>
-      </x:c>
-      <x:c r="D17" s="151" t="str">
-        <x:v>本人</x:v>
-      </x:c>
-      <x:c r="E17" s="151" t="str">
-        <x:v>受信者本人</x:v>
-      </x:c>
-      <x:c r="F17" s="151" t="str">
-        <x:v>認証・本人/共通条件をServiceで判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="155" t="str">
-        <x:v>ControllerのRole表示だけで認可しない。Service層でPermission Code、本人/PJ Member/担当PM等のData範囲、対象Dataの存在を再判定する。</x:v>
-      </x:c>
-      <x:c r="B19" s="155"/>
-      <x:c r="C19" s="155"/>
-      <x:c r="D19" s="155"/>
-      <x:c r="E19" s="155"/>
-      <x:c r="F19" s="155"/>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="155"/>
-      <x:c r="B20" s="155"/>
-      <x:c r="C20" s="155"/>
-      <x:c r="D20" s="155"/>
-      <x:c r="E20" s="155"/>
-      <x:c r="F20" s="155"/>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:F2"/>
-    <x:mergeCell ref="A6:F6"/>
-    <x:mergeCell ref="A19:F20"/>
-  </x:mergeCells>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
 </file>
--- a/基本設計/14_日報と通知_API基本設計書.xlsx
+++ b/基本設計/14_日報と通知_API基本設計書.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R1040268f341a4c0d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R7f037447b0b84dea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_API一覧" sheetId="19" r:id="R9aa9c5ce0d0c47c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_エラーコード" sheetId="22" r:id="Rafdbddf691d44b6c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_API処理・権限" sheetId="24" r:id="R67ce2d0546f042d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_API項目定義" sheetId="25" r:id="Rc817cb6fbd994bc7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_APIサンプル" sheetId="26" r:id="R0d3a6c3c608d49bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R9e7a7151a1c24d10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R66f5dff77f714c4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_API一覧" sheetId="19" r:id="R8e14b787999046aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_エラーコード" sheetId="22" r:id="R49aa914daa64406c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_API処理・権限" sheetId="24" r:id="R0cc6b1a2f1394208"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_API項目定義" sheetId="25" r:id="R0abd6484e2124753"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_APIサンプル" sheetId="26" r:id="R23315fd9854a4562"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1313,7 +1313,7 @@
     <x:row r="11">
       <x:c r="B11"/>
       <x:c r="C11" s="203" t="str">
-        <x:v>Ver.2.5</x:v>
+        <x:v>Ver.2.6</x:v>
       </x:c>
       <x:c r="D11"/>
       <x:c r="E11"/>
@@ -1336,7 +1336,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="D13" s="243" t="str">
-        <x:v>Ver.2.5</x:v>
+        <x:v>Ver.2.6</x:v>
       </x:c>
       <x:c r="E13" s="196"/>
       <x:c r="F13" s="196"/>
@@ -1346,7 +1346,7 @@
         <x:v>改訂日</x:v>
       </x:c>
       <x:c r="D14" s="243" t="str">
-        <x:v>2026-09-24</x:v>
+        <x:v>2026-10-08</x:v>
       </x:c>
       <x:c r="E14" s="196"/>
       <x:c r="F14" s="196"/>
@@ -1511,7 +1511,7 @@
     </x:row>
     <x:row r="4" ht="24" customHeight="1">
       <x:c r="A4" s="246" t="str">
-        <x:v>版数：Ver.2.5    改訂日：2026-09-24    Baseline：BL-2026-09-24</x:v>
+        <x:v>版数：Ver.2.6    改訂日：2026-10-08    Baseline：BL-2026-09-24</x:v>
       </x:c>
       <x:c r="B4" s="63"/>
       <x:c r="C4" s="63"/>
@@ -1909,6 +1909,32 @@
       </x:c>
       <x:c r="H20" s="245" t="str">
         <x:v>BL-2026-09-24。責任者・Review者・承認者はProject Leaderが記入。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="24" hidden="0" customHeight="1">
+      <x:c r="A21" s="245" t="str">
+        <x:v>Ver.2.6</x:v>
+      </x:c>
+      <x:c r="B21" s="245" t="str">
+        <x:v>2026-10-08</x:v>
+      </x:c>
+      <x:c r="C21" s="245" t="str">
+        <x:v>CHG-NTF-20261008-01：通知relatedTypeをTASK／PROJECT／SYSTEMへ統一。REPORT_MISSINGはPROJECT・projectIdを参照。</x:v>
+      </x:c>
+      <x:c r="D21" s="245" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="E21" s="245" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="F21" s="245" t="str">
+        <x:v>未承認</x:v>
+      </x:c>
+      <x:c r="G21" s="245" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="H21" s="245" t="str">
+        <x:v>14・15・16・20の通知関連仕様を整合。基準Baselineは維持。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -8329,7 +8355,7 @@
         <x:v>notifications.content</x:v>
       </x:c>
     </x:row>
-    <x:row r="139" ht="15" hidden="0" customHeight="1">
+    <x:row r="139" ht="24" hidden="0" customHeight="1">
       <x:c r="A139" s="67" t="str">
         <x:v>API-NTF-001</x:v>
       </x:c>
@@ -8352,13 +8378,13 @@
         <x:v>最大50</x:v>
       </x:c>
       <x:c r="H139" s="67" t="str">
-        <x:v>TASK/REPORT/SYSTEM</x:v>
+        <x:v>TASK/PROJECT/SYSTEM</x:v>
       </x:c>
       <x:c r="I139" s="67" t="str">
         <x:v>可</x:v>
       </x:c>
       <x:c r="J139" s="67" t="str">
-        <x:v>関連種別</x:v>
+        <x:v>関連種別。TASKはtaskId、PROJECTはprojectId、SYSTEMはrelatedIdなし。</x:v>
       </x:c>
       <x:c r="K139" s="67" t="str">
         <x:v>notifications.related_type</x:v>
